--- a/events.xlsx
+++ b/events.xlsx
@@ -558,6 +558,9 @@
     <t xml:space="preserve">2026-05-20 11:00
 </t>
   </si>
+  <si>
+    <t>title</t>
+  </si>
 </sst>
 </file>
 
@@ -951,7 +954,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>172</v>

--- a/events.xlsx
+++ b/events.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="2"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet state="visible" name="club" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Karete" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Karate" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Choumeigaoka" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
-  <si>
-    <t>title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>description</t>
   </si>
@@ -43,7 +40,18 @@
 </t>
   </si>
   <si>
-    <t>稽古</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夏祭り	小学校	2026-08-25 16:00	2026-08-25 20:00
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稽古	通町コミュニティセンター 大広間	2026-05-22 16:00	2026-05-22 16:50
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 稽古</t>
   </si>
   <si>
     <t>通町コミュニティセンター 大広間</t>
@@ -53,6 +61,9 @@
   </si>
   <si>
     <t>2026-05-22 16:50</t>
+  </si>
+  <si>
+    <t>夏祭り	小学校	2026-08-25 16:00	2026-08-25 20:00</t>
   </si>
   <si>
     <t>夏祭り</t>
@@ -335,22 +346,22 @@
   <cols>
     <col min="1" max="1" width="11.89" customWidth="1"/>
     <col min="2" max="2" width="13.11" customWidth="1"/>
-    <col min="3" max="3" width="17.22" customWidth="1"/>
+    <col min="3" max="3" width="18.38" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -377,16 +388,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -28367,37 +28378,37 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.21" customWidth="1"/>
-    <col min="3" max="3" width="18.66" customWidth="1"/>
-    <col min="4" max="4" width="19.85" customWidth="1"/>
+    <col min="2" max="2" width="37.53" customWidth="1"/>
+    <col min="3" max="3" width="19.56" customWidth="1"/>
+    <col min="4" max="4" width="19.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
+      <c r="C2" s="0" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -28412,35 +28423,36 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.62" customWidth="1"/>
+    <col min="3" max="3" width="18.59" customWidth="1"/>
+    <col min="4" max="4" width="19.12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/events.xlsx
+++ b/events.xlsx
@@ -1,10 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView activeTab="0"/>
-  </bookViews>
   <sheets>
     <sheet state="visible" name="club" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Karate" sheetId="2" r:id="rId6"/>
@@ -16,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
   <si>
     <t>description</t>
   </si>
@@ -43,66 +40,62 @@
     <t>title</t>
   </si>
   <si>
-    <t xml:space="preserve">夏祭り	小学校	2026-08-25 16:00	2026-08-25 20:00
-</t>
+    <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">稽古	通町コミュニティセンター 大広間	2026-05-22 16:00	2026-05-22 16:50
-</t>
+    <t>空手稽古</t>
   </si>
   <si>
-    <t xml:space="preserve"> 稽古</t>
+    <t>南中山市民センター 体育館</t>
+  </si>
+  <si>
+    <t>中山市民センター ホール</t>
+  </si>
+  <si>
+    <t>宮城野体育館 多目的室</t>
+  </si>
+  <si>
+    <t>東部市民センター 体育館</t>
+  </si>
+  <si>
+    <t>東部市民センター 大広間</t>
+  </si>
+  <si>
+    <t>富沢南集会所</t>
+  </si>
+  <si>
+    <t>2部制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">空手稽古 </t>
   </si>
   <si>
     <t>通町コミュニティセンター 大広間</t>
-  </si>
-  <si>
-    <t>2026-05-22 16:00</t>
-  </si>
-  <si>
-    <t>2026-05-22 16:50</t>
-  </si>
-  <si>
-    <t>夏祭り	小学校	2026-08-25 16:00	2026-08-25 20:00</t>
-  </si>
-  <si>
-    <t>夏祭り</t>
-  </si>
-  <si>
-    <t>小学校</t>
-  </si>
-  <si>
-    <t>2026-08-25 16:00</t>
-  </si>
-  <si>
-    <t>2026-08-25 20:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" mc:Ignorable="x14ac">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);(&quot;$&quot;#,##0)"/>
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red](&quot;$&quot;#,##0)"/>
-    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);(&quot;$&quot;#,##0.00)"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red](&quot;$&quot;#,##0.00)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* (#,##0.00);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* (#,##0.00);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,14 +110,25 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="5">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
@@ -341,19 +345,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.89" customWidth="1"/>
-    <col min="2" max="2" width="13.11" customWidth="1"/>
-    <col min="3" max="3" width="18.38" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="11.89"/>
+    <col customWidth="1" min="2" max="2" width="13.11"/>
+    <col customWidth="1" min="3" max="3" width="17.22"/>
+    <col customWidth="1" min="4" max="4" width="21.0"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,7 +928,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -954,7 +956,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -982,7 +984,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1010,7 +1012,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1038,7 +1040,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1066,7 +1068,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1094,7 +1096,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1122,7 +1124,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1150,7 +1152,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1178,7 +1180,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1206,7 +1208,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1234,7 +1236,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1262,7 +1264,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1290,7 +1292,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1318,7 +1320,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1346,7 +1348,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1374,7 +1376,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1402,7 +1404,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1430,7 +1432,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1458,7 +1460,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1486,7 +1488,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1514,7 +1516,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1542,7 +1544,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1570,7 +1572,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1598,7 +1600,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1626,7 +1628,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1654,7 +1656,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1682,7 +1684,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1710,7 +1712,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1738,7 +1740,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1766,7 +1768,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1794,7 +1796,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1822,7 +1824,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1850,7 +1852,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1878,7 +1880,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1906,7 +1908,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1934,7 +1936,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1962,7 +1964,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1990,7 +1992,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2018,7 +2020,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2046,7 +2048,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2074,7 +2076,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2102,7 +2104,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2130,7 +2132,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2158,7 +2160,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2186,7 +2188,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2214,7 +2216,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2242,7 +2244,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2270,7 +2272,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2298,7 +2300,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2326,7 +2328,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2354,7 +2356,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2382,7 +2384,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2410,7 +2412,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2438,7 +2440,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2466,7 +2468,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2494,7 +2496,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2522,7 +2524,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2550,7 +2552,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2578,7 +2580,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2606,7 +2608,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2634,7 +2636,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2662,7 +2664,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2690,7 +2692,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2718,7 +2720,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2746,7 +2748,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2774,7 +2776,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2802,7 +2804,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2830,7 +2832,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2858,7 +2860,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2886,7 +2888,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2914,7 +2916,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2942,7 +2944,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2970,7 +2972,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2998,7 +3000,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3026,7 +3028,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3054,7 +3056,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3082,7 +3084,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3110,7 +3112,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3138,7 +3140,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3166,7 +3168,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3194,7 +3196,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3222,7 +3224,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3250,7 +3252,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3278,7 +3280,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3306,7 +3308,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3334,7 +3336,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3362,7 +3364,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3390,7 +3392,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3418,7 +3420,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3446,7 +3448,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3474,7 +3476,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3502,7 +3504,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3530,7 +3532,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3558,7 +3560,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3586,7 +3588,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3614,7 +3616,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3642,7 +3644,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3670,7 +3672,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3698,7 +3700,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3726,7 +3728,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3754,7 +3756,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3782,7 +3784,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3810,7 +3812,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3838,7 +3840,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3866,7 +3868,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3894,7 +3896,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3922,7 +3924,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3950,7 +3952,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3978,7 +3980,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4006,7 +4008,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4034,7 +4036,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4062,7 +4064,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4090,7 +4092,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4118,7 +4120,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4146,7 +4148,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4174,7 +4176,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4202,7 +4204,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4230,7 +4232,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4258,7 +4260,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4286,7 +4288,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4314,7 +4316,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4342,7 +4344,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4370,7 +4372,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4398,7 +4400,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4426,7 +4428,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4454,7 +4456,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4482,7 +4484,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4510,7 +4512,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4538,7 +4540,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4566,7 +4568,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4594,7 +4596,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4622,7 +4624,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4650,7 +4652,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4678,7 +4680,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4706,7 +4708,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4734,7 +4736,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4762,7 +4764,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4790,7 +4792,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4818,7 +4820,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4846,7 +4848,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4874,7 +4876,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4902,7 +4904,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4930,7 +4932,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4958,7 +4960,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4986,7 +4988,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5014,7 +5016,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5042,7 +5044,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5070,7 +5072,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5098,7 +5100,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5126,7 +5128,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5154,7 +5156,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5182,7 +5184,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5210,7 +5212,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5238,7 +5240,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5266,7 +5268,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5294,7 +5296,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5322,7 +5324,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5350,7 +5352,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5378,7 +5380,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5406,7 +5408,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5434,7 +5436,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5462,7 +5464,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5490,7 +5492,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5518,7 +5520,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5546,7 +5548,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5574,7 +5576,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5602,7 +5604,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5630,7 +5632,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5658,7 +5660,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5686,7 +5688,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5714,7 +5716,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5742,7 +5744,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5770,7 +5772,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5798,7 +5800,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5826,7 +5828,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5854,7 +5856,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5882,7 +5884,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5910,7 +5912,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5938,7 +5940,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5966,7 +5968,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -5994,7 +5996,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6022,7 +6024,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6050,7 +6052,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6078,7 +6080,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6106,7 +6108,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6134,7 +6136,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6162,7 +6164,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6190,7 +6192,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6218,7 +6220,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6246,7 +6248,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6274,7 +6276,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6302,7 +6304,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6330,7 +6332,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6358,7 +6360,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6386,7 +6388,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6414,7 +6416,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6442,7 +6444,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6470,7 +6472,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6498,7 +6500,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6526,7 +6528,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6554,7 +6556,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="222">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6582,7 +6584,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="223">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6610,7 +6612,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="224">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6638,7 +6640,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6666,7 +6668,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6694,7 +6696,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6722,7 +6724,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -6750,7 +6752,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -6778,7 +6780,7 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -6806,7 +6808,7 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="231">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -6834,7 +6836,7 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="232">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -6862,7 +6864,7 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="233">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -6890,7 +6892,7 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6918,7 +6920,7 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -6946,7 +6948,7 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6974,7 +6976,7 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -7002,7 +7004,7 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -7030,7 +7032,7 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -7058,7 +7060,7 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="240">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7086,7 +7088,7 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="241">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7114,7 +7116,7 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="242">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7142,7 +7144,7 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7170,7 +7172,7 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -7198,7 +7200,7 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -7226,7 +7228,7 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -7254,7 +7256,7 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -7282,7 +7284,7 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -7310,7 +7312,7 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="249">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -7338,7 +7340,7 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="250">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -7366,7 +7368,7 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="251">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -7394,7 +7396,7 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -7422,7 +7424,7 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -7450,7 +7452,7 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="254">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -7478,7 +7480,7 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="255">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -7506,7 +7508,7 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="256">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -7534,7 +7536,7 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="257">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -7562,7 +7564,7 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="258">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -7590,7 +7592,7 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="259">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -7618,7 +7620,7 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="260">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -7646,7 +7648,7 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="261">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -7674,7 +7676,7 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="262">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -7702,7 +7704,7 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="263">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -7730,7 +7732,7 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="264">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -7758,7 +7760,7 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="265">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -7786,7 +7788,7 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="266">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -7814,7 +7816,7 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="267">
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -7842,7 +7844,7 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="268">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -7870,7 +7872,7 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="269">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -7898,7 +7900,7 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="270">
+    <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -7926,7 +7928,7 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="271">
+    <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -7954,7 +7956,7 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="272">
+    <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -7982,7 +7984,7 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="273">
+    <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -8010,7 +8012,7 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="274">
+    <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -8038,7 +8040,7 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="275">
+    <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -8066,7 +8068,7 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="276">
+    <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -8094,7 +8096,7 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="277">
+    <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -8122,7 +8124,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="278">
+    <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -8150,7 +8152,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="279">
+    <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -8178,7 +8180,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="280">
+    <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -8206,7 +8208,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="281">
+    <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -8234,7 +8236,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="282">
+    <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -8262,7 +8264,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="283">
+    <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -8290,7 +8292,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="284">
+    <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -8318,7 +8320,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="285">
+    <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -8346,7 +8348,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="286">
+    <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -8374,7 +8376,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="287">
+    <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -8402,7 +8404,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="288">
+    <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -8430,7 +8432,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="289">
+    <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -8458,7 +8460,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="290">
+    <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -8486,7 +8488,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="291">
+    <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -8514,7 +8516,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="292">
+    <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -8542,7 +8544,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="293">
+    <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -8570,7 +8572,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="294">
+    <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -8598,7 +8600,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="295">
+    <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -8626,7 +8628,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="296">
+    <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -8654,7 +8656,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="297">
+    <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -8682,7 +8684,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="298">
+    <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -8710,7 +8712,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="299">
+    <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -8738,7 +8740,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="300">
+    <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -8766,7 +8768,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="301">
+    <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -8794,7 +8796,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="302">
+    <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -8822,7 +8824,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="303">
+    <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -8850,7 +8852,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="304">
+    <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -8878,7 +8880,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="305">
+    <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -8906,7 +8908,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="306">
+    <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -8934,7 +8936,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="307">
+    <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -8962,7 +8964,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="308">
+    <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -8990,7 +8992,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="309">
+    <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -9018,7 +9020,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="310">
+    <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -9046,7 +9048,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="311">
+    <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -9074,7 +9076,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="312">
+    <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -9102,7 +9104,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="313">
+    <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -9130,7 +9132,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="314">
+    <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -9158,7 +9160,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="315">
+    <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -9186,7 +9188,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="316">
+    <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -9214,7 +9216,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="317">
+    <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -9242,7 +9244,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="318">
+    <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -9270,7 +9272,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="319">
+    <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -9298,7 +9300,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="320">
+    <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -9326,7 +9328,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="321">
+    <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -9354,7 +9356,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="322">
+    <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -9382,7 +9384,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="323">
+    <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -9410,7 +9412,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="324">
+    <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -9438,7 +9440,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="325">
+    <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -9466,7 +9468,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="326">
+    <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -9494,7 +9496,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="327">
+    <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -9522,7 +9524,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="328">
+    <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -9550,7 +9552,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="329">
+    <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -9578,7 +9580,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="330">
+    <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -9606,7 +9608,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="331">
+    <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -9634,7 +9636,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="332">
+    <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -9662,7 +9664,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="333">
+    <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -9690,7 +9692,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="334">
+    <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -9718,7 +9720,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="335">
+    <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -9746,7 +9748,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="336">
+    <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -9774,7 +9776,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="337">
+    <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -9802,7 +9804,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="338">
+    <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -9830,7 +9832,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="339">
+    <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -9858,7 +9860,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="340">
+    <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -9886,7 +9888,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="341">
+    <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -9914,7 +9916,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="342">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -9942,7 +9944,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="343">
+    <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -9970,7 +9972,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="344">
+    <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -9998,7 +10000,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="345">
+    <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -10026,7 +10028,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="346">
+    <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -10054,7 +10056,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="347">
+    <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -10082,7 +10084,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="348">
+    <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -10110,7 +10112,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="349">
+    <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -10138,7 +10140,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="350">
+    <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -10166,7 +10168,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="351">
+    <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -10194,7 +10196,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="352">
+    <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -10222,7 +10224,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="353">
+    <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -10250,7 +10252,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="354">
+    <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -10278,7 +10280,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="355">
+    <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -10306,7 +10308,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="356">
+    <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -10334,7 +10336,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="357">
+    <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -10362,7 +10364,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="358">
+    <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -10390,7 +10392,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="359">
+    <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -10418,7 +10420,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="360">
+    <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -10446,7 +10448,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="361">
+    <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -10474,7 +10476,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="362">
+    <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -10502,7 +10504,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="363">
+    <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -10530,7 +10532,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="364">
+    <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -10558,7 +10560,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="365">
+    <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -10586,7 +10588,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="366">
+    <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -10614,7 +10616,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="367">
+    <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -10642,7 +10644,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="368">
+    <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -10670,7 +10672,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="369">
+    <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -10698,7 +10700,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="370">
+    <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -10726,7 +10728,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="371">
+    <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -10754,7 +10756,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="372">
+    <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -10782,7 +10784,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="373">
+    <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -10810,7 +10812,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="374">
+    <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -10838,7 +10840,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="375">
+    <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -10866,7 +10868,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="376">
+    <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -10894,7 +10896,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="377">
+    <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -10922,7 +10924,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="378">
+    <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -10950,7 +10952,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="379">
+    <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -10978,7 +10980,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="380">
+    <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -11006,7 +11008,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="381">
+    <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -11034,7 +11036,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="382">
+    <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -11062,7 +11064,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="383">
+    <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -11090,7 +11092,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="384">
+    <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -11118,7 +11120,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="385">
+    <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -11146,7 +11148,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="386">
+    <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -11174,7 +11176,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="387">
+    <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -11202,7 +11204,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="388">
+    <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -11230,7 +11232,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="389">
+    <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -11258,7 +11260,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="390">
+    <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -11286,7 +11288,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="391">
+    <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -11314,7 +11316,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="392">
+    <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -11342,7 +11344,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="393">
+    <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -11370,7 +11372,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="394">
+    <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -11398,7 +11400,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="395">
+    <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -11426,7 +11428,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="396">
+    <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -11454,7 +11456,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="397">
+    <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -11482,7 +11484,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="398">
+    <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -11510,7 +11512,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="399">
+    <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -11538,7 +11540,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="400">
+    <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -11566,7 +11568,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="401">
+    <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -11594,7 +11596,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="402">
+    <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -11622,7 +11624,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="403">
+    <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -11650,7 +11652,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="404">
+    <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -11678,7 +11680,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="405">
+    <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -11706,7 +11708,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="406">
+    <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -11734,7 +11736,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="407">
+    <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -11762,7 +11764,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="408">
+    <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -11790,7 +11792,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="409">
+    <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -11818,7 +11820,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="410">
+    <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -11846,7 +11848,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="411">
+    <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -11874,7 +11876,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="412">
+    <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -11902,7 +11904,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="413">
+    <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -11930,7 +11932,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="414">
+    <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -11958,7 +11960,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="415">
+    <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -11986,7 +11988,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="416">
+    <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -12014,7 +12016,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="417">
+    <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -12042,7 +12044,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="418">
+    <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -12070,7 +12072,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="419">
+    <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -12098,7 +12100,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="420">
+    <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -12126,7 +12128,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="421">
+    <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -12154,7 +12156,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="422">
+    <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -12182,7 +12184,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="423">
+    <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -12210,7 +12212,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="424">
+    <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -12238,7 +12240,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="425">
+    <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -12266,7 +12268,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="426">
+    <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -12294,7 +12296,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="427">
+    <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -12322,7 +12324,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="428">
+    <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -12350,7 +12352,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="429">
+    <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -12378,7 +12380,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="430">
+    <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -12406,7 +12408,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="431">
+    <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -12434,7 +12436,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="432">
+    <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -12462,7 +12464,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="433">
+    <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -12490,7 +12492,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="434">
+    <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -12518,7 +12520,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="435">
+    <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -12546,7 +12548,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="436">
+    <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -12574,7 +12576,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="437">
+    <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -12602,7 +12604,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="438">
+    <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -12630,7 +12632,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="439">
+    <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -12658,7 +12660,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="440">
+    <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -12686,7 +12688,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="441">
+    <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -12714,7 +12716,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="442">
+    <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -12742,7 +12744,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="443">
+    <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -12770,7 +12772,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="444">
+    <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -12798,7 +12800,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="445">
+    <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -12826,7 +12828,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="446">
+    <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -12854,7 +12856,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="447">
+    <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -12882,7 +12884,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="448">
+    <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -12910,7 +12912,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="449">
+    <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -12938,7 +12940,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="450">
+    <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -12966,7 +12968,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="451">
+    <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -12994,7 +12996,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="452">
+    <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -13022,7 +13024,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="453">
+    <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -13050,7 +13052,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="454">
+    <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -13078,7 +13080,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="455">
+    <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -13106,7 +13108,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="456">
+    <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -13134,7 +13136,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="457">
+    <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -13162,7 +13164,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="458">
+    <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -13190,7 +13192,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="459">
+    <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -13218,7 +13220,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="460">
+    <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -13246,7 +13248,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="461">
+    <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -13274,7 +13276,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="462">
+    <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -13302,7 +13304,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="463">
+    <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -13330,7 +13332,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="464">
+    <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -13358,7 +13360,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="465">
+    <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -13386,7 +13388,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="466">
+    <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -13414,7 +13416,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="467">
+    <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -13442,7 +13444,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="468">
+    <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -13470,7 +13472,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="469">
+    <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -13498,7 +13500,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="470">
+    <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -13526,7 +13528,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="471">
+    <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -13554,7 +13556,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="472">
+    <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -13582,7 +13584,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="473">
+    <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -13610,7 +13612,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="474">
+    <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -13638,7 +13640,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="475">
+    <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -13666,7 +13668,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="476">
+    <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -13694,7 +13696,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="477">
+    <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -13722,7 +13724,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="478">
+    <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -13750,7 +13752,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="479">
+    <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -13778,7 +13780,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="480">
+    <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -13806,7 +13808,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="481">
+    <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -13834,7 +13836,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="482">
+    <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -13862,7 +13864,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="483">
+    <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -13890,7 +13892,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="484">
+    <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -13918,7 +13920,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="485">
+    <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -13946,7 +13948,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="486">
+    <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -13974,7 +13976,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="487">
+    <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -14002,7 +14004,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="488">
+    <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -14030,7 +14032,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="489">
+    <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -14058,7 +14060,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="490">
+    <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -14086,7 +14088,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="491">
+    <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -14114,7 +14116,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="492">
+    <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -14142,7 +14144,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="493">
+    <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -14170,7 +14172,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="494">
+    <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -14198,7 +14200,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="495">
+    <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -14226,7 +14228,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="496">
+    <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -14254,7 +14256,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="497">
+    <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -14282,7 +14284,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="498">
+    <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -14310,7 +14312,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="499">
+    <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -14338,7 +14340,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="500">
+    <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -14366,7 +14368,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="501">
+    <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -14394,7 +14396,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="502">
+    <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -14422,7 +14424,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="503">
+    <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -14450,7 +14452,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="504">
+    <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -14478,7 +14480,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="505">
+    <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -14506,7 +14508,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="506">
+    <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -14534,7 +14536,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="507">
+    <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -14562,7 +14564,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="508">
+    <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -14590,7 +14592,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="509">
+    <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -14618,7 +14620,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="510">
+    <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -14646,7 +14648,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="511">
+    <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -14674,7 +14676,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="512">
+    <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -14702,7 +14704,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="513">
+    <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -14730,7 +14732,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="514">
+    <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -14758,7 +14760,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="515">
+    <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -14786,7 +14788,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="516">
+    <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -14814,7 +14816,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="517">
+    <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -14842,7 +14844,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="518">
+    <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -14870,7 +14872,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="519">
+    <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -14898,7 +14900,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="520">
+    <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -14926,7 +14928,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="521">
+    <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -14954,7 +14956,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="522">
+    <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -14982,7 +14984,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="523">
+    <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -15010,7 +15012,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="524">
+    <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -15038,7 +15040,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="525">
+    <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -15066,7 +15068,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="526">
+    <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -15094,7 +15096,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="527">
+    <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -15122,7 +15124,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="528">
+    <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -15150,7 +15152,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="529">
+    <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -15178,7 +15180,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="530">
+    <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -15206,7 +15208,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="531">
+    <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -15234,7 +15236,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="532">
+    <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -15262,7 +15264,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="533">
+    <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -15290,7 +15292,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="534">
+    <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -15318,7 +15320,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="535">
+    <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -15346,7 +15348,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="536">
+    <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -15374,7 +15376,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="537">
+    <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -15402,7 +15404,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="538">
+    <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -15430,7 +15432,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="539">
+    <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -15458,7 +15460,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="540">
+    <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -15486,7 +15488,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="541">
+    <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -15514,7 +15516,7 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="542">
+    <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -15542,7 +15544,7 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="543">
+    <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -15570,7 +15572,7 @@
       <c r="Y543" s="1"/>
       <c r="Z543" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="544">
+    <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -15598,7 +15600,7 @@
       <c r="Y544" s="1"/>
       <c r="Z544" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="545">
+    <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -15626,7 +15628,7 @@
       <c r="Y545" s="1"/>
       <c r="Z545" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="546">
+    <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -15654,7 +15656,7 @@
       <c r="Y546" s="1"/>
       <c r="Z546" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="547">
+    <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -15682,7 +15684,7 @@
       <c r="Y547" s="1"/>
       <c r="Z547" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="548">
+    <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -15710,7 +15712,7 @@
       <c r="Y548" s="1"/>
       <c r="Z548" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="549">
+    <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -15738,7 +15740,7 @@
       <c r="Y549" s="1"/>
       <c r="Z549" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="550">
+    <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -15766,7 +15768,7 @@
       <c r="Y550" s="1"/>
       <c r="Z550" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="551">
+    <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -15794,7 +15796,7 @@
       <c r="Y551" s="1"/>
       <c r="Z551" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="552">
+    <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -15822,7 +15824,7 @@
       <c r="Y552" s="1"/>
       <c r="Z552" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="553">
+    <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -15850,7 +15852,7 @@
       <c r="Y553" s="1"/>
       <c r="Z553" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="554">
+    <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -15878,7 +15880,7 @@
       <c r="Y554" s="1"/>
       <c r="Z554" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="555">
+    <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -15906,7 +15908,7 @@
       <c r="Y555" s="1"/>
       <c r="Z555" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="556">
+    <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -15934,7 +15936,7 @@
       <c r="Y556" s="1"/>
       <c r="Z556" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="557">
+    <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -15962,7 +15964,7 @@
       <c r="Y557" s="1"/>
       <c r="Z557" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="558">
+    <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -15990,7 +15992,7 @@
       <c r="Y558" s="1"/>
       <c r="Z558" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="559">
+    <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -16018,7 +16020,7 @@
       <c r="Y559" s="1"/>
       <c r="Z559" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="560">
+    <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -16046,7 +16048,7 @@
       <c r="Y560" s="1"/>
       <c r="Z560" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="561">
+    <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -16074,7 +16076,7 @@
       <c r="Y561" s="1"/>
       <c r="Z561" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="562">
+    <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -16102,7 +16104,7 @@
       <c r="Y562" s="1"/>
       <c r="Z562" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="563">
+    <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -16130,7 +16132,7 @@
       <c r="Y563" s="1"/>
       <c r="Z563" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="564">
+    <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -16158,7 +16160,7 @@
       <c r="Y564" s="1"/>
       <c r="Z564" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="565">
+    <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -16186,7 +16188,7 @@
       <c r="Y565" s="1"/>
       <c r="Z565" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="566">
+    <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -16214,7 +16216,7 @@
       <c r="Y566" s="1"/>
       <c r="Z566" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="567">
+    <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -16242,7 +16244,7 @@
       <c r="Y567" s="1"/>
       <c r="Z567" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="568">
+    <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -16270,7 +16272,7 @@
       <c r="Y568" s="1"/>
       <c r="Z568" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="569">
+    <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -16298,7 +16300,7 @@
       <c r="Y569" s="1"/>
       <c r="Z569" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="570">
+    <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -16326,7 +16328,7 @@
       <c r="Y570" s="1"/>
       <c r="Z570" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="571">
+    <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -16354,7 +16356,7 @@
       <c r="Y571" s="1"/>
       <c r="Z571" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="572">
+    <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -16382,7 +16384,7 @@
       <c r="Y572" s="1"/>
       <c r="Z572" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="573">
+    <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -16410,7 +16412,7 @@
       <c r="Y573" s="1"/>
       <c r="Z573" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="574">
+    <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -16438,7 +16440,7 @@
       <c r="Y574" s="1"/>
       <c r="Z574" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="575">
+    <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -16466,7 +16468,7 @@
       <c r="Y575" s="1"/>
       <c r="Z575" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="576">
+    <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -16494,7 +16496,7 @@
       <c r="Y576" s="1"/>
       <c r="Z576" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="577">
+    <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -16522,7 +16524,7 @@
       <c r="Y577" s="1"/>
       <c r="Z577" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="578">
+    <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -16550,7 +16552,7 @@
       <c r="Y578" s="1"/>
       <c r="Z578" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="579">
+    <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -16578,7 +16580,7 @@
       <c r="Y579" s="1"/>
       <c r="Z579" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="580">
+    <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -16606,7 +16608,7 @@
       <c r="Y580" s="1"/>
       <c r="Z580" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="581">
+    <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -16634,7 +16636,7 @@
       <c r="Y581" s="1"/>
       <c r="Z581" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="582">
+    <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -16662,7 +16664,7 @@
       <c r="Y582" s="1"/>
       <c r="Z582" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="583">
+    <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -16690,7 +16692,7 @@
       <c r="Y583" s="1"/>
       <c r="Z583" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="584">
+    <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -16718,7 +16720,7 @@
       <c r="Y584" s="1"/>
       <c r="Z584" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="585">
+    <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -16746,7 +16748,7 @@
       <c r="Y585" s="1"/>
       <c r="Z585" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="586">
+    <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -16774,7 +16776,7 @@
       <c r="Y586" s="1"/>
       <c r="Z586" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="587">
+    <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -16802,7 +16804,7 @@
       <c r="Y587" s="1"/>
       <c r="Z587" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="588">
+    <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -16830,7 +16832,7 @@
       <c r="Y588" s="1"/>
       <c r="Z588" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="589">
+    <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -16858,7 +16860,7 @@
       <c r="Y589" s="1"/>
       <c r="Z589" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="590">
+    <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -16886,7 +16888,7 @@
       <c r="Y590" s="1"/>
       <c r="Z590" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="591">
+    <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -16914,7 +16916,7 @@
       <c r="Y591" s="1"/>
       <c r="Z591" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="592">
+    <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -16942,7 +16944,7 @@
       <c r="Y592" s="1"/>
       <c r="Z592" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="593">
+    <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -16970,7 +16972,7 @@
       <c r="Y593" s="1"/>
       <c r="Z593" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="594">
+    <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -16998,7 +17000,7 @@
       <c r="Y594" s="1"/>
       <c r="Z594" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="595">
+    <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -17026,7 +17028,7 @@
       <c r="Y595" s="1"/>
       <c r="Z595" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="596">
+    <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -17054,7 +17056,7 @@
       <c r="Y596" s="1"/>
       <c r="Z596" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="597">
+    <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -17082,7 +17084,7 @@
       <c r="Y597" s="1"/>
       <c r="Z597" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="598">
+    <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -17110,7 +17112,7 @@
       <c r="Y598" s="1"/>
       <c r="Z598" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="599">
+    <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -17138,7 +17140,7 @@
       <c r="Y599" s="1"/>
       <c r="Z599" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="600">
+    <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -17166,7 +17168,7 @@
       <c r="Y600" s="1"/>
       <c r="Z600" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="601">
+    <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -17194,7 +17196,7 @@
       <c r="Y601" s="1"/>
       <c r="Z601" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="602">
+    <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -17222,7 +17224,7 @@
       <c r="Y602" s="1"/>
       <c r="Z602" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="603">
+    <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -17250,7 +17252,7 @@
       <c r="Y603" s="1"/>
       <c r="Z603" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="604">
+    <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -17278,7 +17280,7 @@
       <c r="Y604" s="1"/>
       <c r="Z604" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="605">
+    <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -17306,7 +17308,7 @@
       <c r="Y605" s="1"/>
       <c r="Z605" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="606">
+    <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -17334,7 +17336,7 @@
       <c r="Y606" s="1"/>
       <c r="Z606" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="607">
+    <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -17362,7 +17364,7 @@
       <c r="Y607" s="1"/>
       <c r="Z607" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="608">
+    <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -17390,7 +17392,7 @@
       <c r="Y608" s="1"/>
       <c r="Z608" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="609">
+    <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -17418,7 +17420,7 @@
       <c r="Y609" s="1"/>
       <c r="Z609" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="610">
+    <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -17446,7 +17448,7 @@
       <c r="Y610" s="1"/>
       <c r="Z610" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="611">
+    <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -17474,7 +17476,7 @@
       <c r="Y611" s="1"/>
       <c r="Z611" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="612">
+    <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -17502,7 +17504,7 @@
       <c r="Y612" s="1"/>
       <c r="Z612" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="613">
+    <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -17530,7 +17532,7 @@
       <c r="Y613" s="1"/>
       <c r="Z613" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="614">
+    <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -17558,7 +17560,7 @@
       <c r="Y614" s="1"/>
       <c r="Z614" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="615">
+    <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -17586,7 +17588,7 @@
       <c r="Y615" s="1"/>
       <c r="Z615" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="616">
+    <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -17614,7 +17616,7 @@
       <c r="Y616" s="1"/>
       <c r="Z616" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="617">
+    <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -17642,7 +17644,7 @@
       <c r="Y617" s="1"/>
       <c r="Z617" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="618">
+    <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -17670,7 +17672,7 @@
       <c r="Y618" s="1"/>
       <c r="Z618" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="619">
+    <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -17698,7 +17700,7 @@
       <c r="Y619" s="1"/>
       <c r="Z619" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="620">
+    <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -17726,7 +17728,7 @@
       <c r="Y620" s="1"/>
       <c r="Z620" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="621">
+    <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -17754,7 +17756,7 @@
       <c r="Y621" s="1"/>
       <c r="Z621" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="622">
+    <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -17782,7 +17784,7 @@
       <c r="Y622" s="1"/>
       <c r="Z622" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="623">
+    <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -17810,7 +17812,7 @@
       <c r="Y623" s="1"/>
       <c r="Z623" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="624">
+    <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -17838,7 +17840,7 @@
       <c r="Y624" s="1"/>
       <c r="Z624" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="625">
+    <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -17866,7 +17868,7 @@
       <c r="Y625" s="1"/>
       <c r="Z625" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="626">
+    <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -17894,7 +17896,7 @@
       <c r="Y626" s="1"/>
       <c r="Z626" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="627">
+    <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -17922,7 +17924,7 @@
       <c r="Y627" s="1"/>
       <c r="Z627" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="628">
+    <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -17950,7 +17952,7 @@
       <c r="Y628" s="1"/>
       <c r="Z628" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="629">
+    <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -17978,7 +17980,7 @@
       <c r="Y629" s="1"/>
       <c r="Z629" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="630">
+    <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -18006,7 +18008,7 @@
       <c r="Y630" s="1"/>
       <c r="Z630" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="631">
+    <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -18034,7 +18036,7 @@
       <c r="Y631" s="1"/>
       <c r="Z631" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="632">
+    <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -18062,7 +18064,7 @@
       <c r="Y632" s="1"/>
       <c r="Z632" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="633">
+    <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -18090,7 +18092,7 @@
       <c r="Y633" s="1"/>
       <c r="Z633" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="634">
+    <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -18118,7 +18120,7 @@
       <c r="Y634" s="1"/>
       <c r="Z634" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="635">
+    <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -18146,7 +18148,7 @@
       <c r="Y635" s="1"/>
       <c r="Z635" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="636">
+    <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -18174,7 +18176,7 @@
       <c r="Y636" s="1"/>
       <c r="Z636" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="637">
+    <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -18202,7 +18204,7 @@
       <c r="Y637" s="1"/>
       <c r="Z637" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="638">
+    <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -18230,7 +18232,7 @@
       <c r="Y638" s="1"/>
       <c r="Z638" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="639">
+    <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -18258,7 +18260,7 @@
       <c r="Y639" s="1"/>
       <c r="Z639" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="640">
+    <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -18286,7 +18288,7 @@
       <c r="Y640" s="1"/>
       <c r="Z640" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="641">
+    <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -18314,7 +18316,7 @@
       <c r="Y641" s="1"/>
       <c r="Z641" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="642">
+    <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -18342,7 +18344,7 @@
       <c r="Y642" s="1"/>
       <c r="Z642" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="643">
+    <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -18370,7 +18372,7 @@
       <c r="Y643" s="1"/>
       <c r="Z643" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="644">
+    <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -18398,7 +18400,7 @@
       <c r="Y644" s="1"/>
       <c r="Z644" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="645">
+    <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -18426,7 +18428,7 @@
       <c r="Y645" s="1"/>
       <c r="Z645" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="646">
+    <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -18454,7 +18456,7 @@
       <c r="Y646" s="1"/>
       <c r="Z646" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="647">
+    <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -18482,7 +18484,7 @@
       <c r="Y647" s="1"/>
       <c r="Z647" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="648">
+    <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -18510,7 +18512,7 @@
       <c r="Y648" s="1"/>
       <c r="Z648" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="649">
+    <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -18538,7 +18540,7 @@
       <c r="Y649" s="1"/>
       <c r="Z649" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="650">
+    <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -18566,7 +18568,7 @@
       <c r="Y650" s="1"/>
       <c r="Z650" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="651">
+    <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -18594,7 +18596,7 @@
       <c r="Y651" s="1"/>
       <c r="Z651" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="652">
+    <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -18622,7 +18624,7 @@
       <c r="Y652" s="1"/>
       <c r="Z652" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="653">
+    <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -18650,7 +18652,7 @@
       <c r="Y653" s="1"/>
       <c r="Z653" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="654">
+    <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -18678,7 +18680,7 @@
       <c r="Y654" s="1"/>
       <c r="Z654" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="655">
+    <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -18706,7 +18708,7 @@
       <c r="Y655" s="1"/>
       <c r="Z655" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="656">
+    <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -18734,7 +18736,7 @@
       <c r="Y656" s="1"/>
       <c r="Z656" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="657">
+    <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -18762,7 +18764,7 @@
       <c r="Y657" s="1"/>
       <c r="Z657" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="658">
+    <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -18790,7 +18792,7 @@
       <c r="Y658" s="1"/>
       <c r="Z658" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="659">
+    <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -18818,7 +18820,7 @@
       <c r="Y659" s="1"/>
       <c r="Z659" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="660">
+    <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -18846,7 +18848,7 @@
       <c r="Y660" s="1"/>
       <c r="Z660" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="661">
+    <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -18874,7 +18876,7 @@
       <c r="Y661" s="1"/>
       <c r="Z661" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="662">
+    <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -18902,7 +18904,7 @@
       <c r="Y662" s="1"/>
       <c r="Z662" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="663">
+    <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -18930,7 +18932,7 @@
       <c r="Y663" s="1"/>
       <c r="Z663" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="664">
+    <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -18958,7 +18960,7 @@
       <c r="Y664" s="1"/>
       <c r="Z664" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="665">
+    <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -18986,7 +18988,7 @@
       <c r="Y665" s="1"/>
       <c r="Z665" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="666">
+    <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -19014,7 +19016,7 @@
       <c r="Y666" s="1"/>
       <c r="Z666" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="667">
+    <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -19042,7 +19044,7 @@
       <c r="Y667" s="1"/>
       <c r="Z667" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="668">
+    <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -19070,7 +19072,7 @@
       <c r="Y668" s="1"/>
       <c r="Z668" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="669">
+    <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -19098,7 +19100,7 @@
       <c r="Y669" s="1"/>
       <c r="Z669" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="670">
+    <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -19126,7 +19128,7 @@
       <c r="Y670" s="1"/>
       <c r="Z670" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="671">
+    <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -19154,7 +19156,7 @@
       <c r="Y671" s="1"/>
       <c r="Z671" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="672">
+    <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -19182,7 +19184,7 @@
       <c r="Y672" s="1"/>
       <c r="Z672" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="673">
+    <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -19210,7 +19212,7 @@
       <c r="Y673" s="1"/>
       <c r="Z673" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="674">
+    <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -19238,7 +19240,7 @@
       <c r="Y674" s="1"/>
       <c r="Z674" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="675">
+    <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -19266,7 +19268,7 @@
       <c r="Y675" s="1"/>
       <c r="Z675" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="676">
+    <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -19294,7 +19296,7 @@
       <c r="Y676" s="1"/>
       <c r="Z676" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="677">
+    <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -19322,7 +19324,7 @@
       <c r="Y677" s="1"/>
       <c r="Z677" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="678">
+    <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -19350,7 +19352,7 @@
       <c r="Y678" s="1"/>
       <c r="Z678" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="679">
+    <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -19378,7 +19380,7 @@
       <c r="Y679" s="1"/>
       <c r="Z679" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="680">
+    <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -19406,7 +19408,7 @@
       <c r="Y680" s="1"/>
       <c r="Z680" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="681">
+    <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -19434,7 +19436,7 @@
       <c r="Y681" s="1"/>
       <c r="Z681" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="682">
+    <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -19462,7 +19464,7 @@
       <c r="Y682" s="1"/>
       <c r="Z682" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="683">
+    <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -19490,7 +19492,7 @@
       <c r="Y683" s="1"/>
       <c r="Z683" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="684">
+    <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -19518,7 +19520,7 @@
       <c r="Y684" s="1"/>
       <c r="Z684" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="685">
+    <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -19546,7 +19548,7 @@
       <c r="Y685" s="1"/>
       <c r="Z685" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="686">
+    <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -19574,7 +19576,7 @@
       <c r="Y686" s="1"/>
       <c r="Z686" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="687">
+    <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -19602,7 +19604,7 @@
       <c r="Y687" s="1"/>
       <c r="Z687" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="688">
+    <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -19630,7 +19632,7 @@
       <c r="Y688" s="1"/>
       <c r="Z688" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="689">
+    <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -19658,7 +19660,7 @@
       <c r="Y689" s="1"/>
       <c r="Z689" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="690">
+    <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -19686,7 +19688,7 @@
       <c r="Y690" s="1"/>
       <c r="Z690" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="691">
+    <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -19714,7 +19716,7 @@
       <c r="Y691" s="1"/>
       <c r="Z691" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="692">
+    <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -19742,7 +19744,7 @@
       <c r="Y692" s="1"/>
       <c r="Z692" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="693">
+    <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -19770,7 +19772,7 @@
       <c r="Y693" s="1"/>
       <c r="Z693" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="694">
+    <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -19798,7 +19800,7 @@
       <c r="Y694" s="1"/>
       <c r="Z694" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="695">
+    <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -19826,7 +19828,7 @@
       <c r="Y695" s="1"/>
       <c r="Z695" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="696">
+    <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -19854,7 +19856,7 @@
       <c r="Y696" s="1"/>
       <c r="Z696" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="697">
+    <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -19882,7 +19884,7 @@
       <c r="Y697" s="1"/>
       <c r="Z697" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="698">
+    <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -19910,7 +19912,7 @@
       <c r="Y698" s="1"/>
       <c r="Z698" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="699">
+    <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -19938,7 +19940,7 @@
       <c r="Y699" s="1"/>
       <c r="Z699" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="700">
+    <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -19966,7 +19968,7 @@
       <c r="Y700" s="1"/>
       <c r="Z700" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="701">
+    <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -19994,7 +19996,7 @@
       <c r="Y701" s="1"/>
       <c r="Z701" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="702">
+    <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -20022,7 +20024,7 @@
       <c r="Y702" s="1"/>
       <c r="Z702" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="703">
+    <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -20050,7 +20052,7 @@
       <c r="Y703" s="1"/>
       <c r="Z703" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="704">
+    <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -20078,7 +20080,7 @@
       <c r="Y704" s="1"/>
       <c r="Z704" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="705">
+    <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -20106,7 +20108,7 @@
       <c r="Y705" s="1"/>
       <c r="Z705" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="706">
+    <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -20134,7 +20136,7 @@
       <c r="Y706" s="1"/>
       <c r="Z706" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="707">
+    <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -20162,7 +20164,7 @@
       <c r="Y707" s="1"/>
       <c r="Z707" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="708">
+    <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -20190,7 +20192,7 @@
       <c r="Y708" s="1"/>
       <c r="Z708" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="709">
+    <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -20218,7 +20220,7 @@
       <c r="Y709" s="1"/>
       <c r="Z709" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="710">
+    <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -20246,7 +20248,7 @@
       <c r="Y710" s="1"/>
       <c r="Z710" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="711">
+    <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -20274,7 +20276,7 @@
       <c r="Y711" s="1"/>
       <c r="Z711" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="712">
+    <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -20302,7 +20304,7 @@
       <c r="Y712" s="1"/>
       <c r="Z712" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="713">
+    <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -20330,7 +20332,7 @@
       <c r="Y713" s="1"/>
       <c r="Z713" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="714">
+    <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -20358,7 +20360,7 @@
       <c r="Y714" s="1"/>
       <c r="Z714" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="715">
+    <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -20386,7 +20388,7 @@
       <c r="Y715" s="1"/>
       <c r="Z715" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="716">
+    <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -20414,7 +20416,7 @@
       <c r="Y716" s="1"/>
       <c r="Z716" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="717">
+    <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -20442,7 +20444,7 @@
       <c r="Y717" s="1"/>
       <c r="Z717" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="718">
+    <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -20470,7 +20472,7 @@
       <c r="Y718" s="1"/>
       <c r="Z718" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="719">
+    <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -20498,7 +20500,7 @@
       <c r="Y719" s="1"/>
       <c r="Z719" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="720">
+    <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -20526,7 +20528,7 @@
       <c r="Y720" s="1"/>
       <c r="Z720" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="721">
+    <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -20554,7 +20556,7 @@
       <c r="Y721" s="1"/>
       <c r="Z721" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="722">
+    <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -20582,7 +20584,7 @@
       <c r="Y722" s="1"/>
       <c r="Z722" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="723">
+    <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -20610,7 +20612,7 @@
       <c r="Y723" s="1"/>
       <c r="Z723" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="724">
+    <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -20638,7 +20640,7 @@
       <c r="Y724" s="1"/>
       <c r="Z724" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="725">
+    <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -20666,7 +20668,7 @@
       <c r="Y725" s="1"/>
       <c r="Z725" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="726">
+    <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -20694,7 +20696,7 @@
       <c r="Y726" s="1"/>
       <c r="Z726" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="727">
+    <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -20722,7 +20724,7 @@
       <c r="Y727" s="1"/>
       <c r="Z727" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="728">
+    <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -20750,7 +20752,7 @@
       <c r="Y728" s="1"/>
       <c r="Z728" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="729">
+    <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -20778,7 +20780,7 @@
       <c r="Y729" s="1"/>
       <c r="Z729" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="730">
+    <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -20806,7 +20808,7 @@
       <c r="Y730" s="1"/>
       <c r="Z730" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="731">
+    <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -20834,7 +20836,7 @@
       <c r="Y731" s="1"/>
       <c r="Z731" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="732">
+    <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -20862,7 +20864,7 @@
       <c r="Y732" s="1"/>
       <c r="Z732" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="733">
+    <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -20890,7 +20892,7 @@
       <c r="Y733" s="1"/>
       <c r="Z733" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="734">
+    <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -20918,7 +20920,7 @@
       <c r="Y734" s="1"/>
       <c r="Z734" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="735">
+    <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -20946,7 +20948,7 @@
       <c r="Y735" s="1"/>
       <c r="Z735" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="736">
+    <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -20974,7 +20976,7 @@
       <c r="Y736" s="1"/>
       <c r="Z736" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="737">
+    <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -21002,7 +21004,7 @@
       <c r="Y737" s="1"/>
       <c r="Z737" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="738">
+    <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -21030,7 +21032,7 @@
       <c r="Y738" s="1"/>
       <c r="Z738" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="739">
+    <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -21058,7 +21060,7 @@
       <c r="Y739" s="1"/>
       <c r="Z739" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="740">
+    <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -21086,7 +21088,7 @@
       <c r="Y740" s="1"/>
       <c r="Z740" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="741">
+    <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -21114,7 +21116,7 @@
       <c r="Y741" s="1"/>
       <c r="Z741" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="742">
+    <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -21142,7 +21144,7 @@
       <c r="Y742" s="1"/>
       <c r="Z742" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="743">
+    <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -21170,7 +21172,7 @@
       <c r="Y743" s="1"/>
       <c r="Z743" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="744">
+    <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -21198,7 +21200,7 @@
       <c r="Y744" s="1"/>
       <c r="Z744" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="745">
+    <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -21226,7 +21228,7 @@
       <c r="Y745" s="1"/>
       <c r="Z745" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="746">
+    <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -21254,7 +21256,7 @@
       <c r="Y746" s="1"/>
       <c r="Z746" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="747">
+    <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -21282,7 +21284,7 @@
       <c r="Y747" s="1"/>
       <c r="Z747" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="748">
+    <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -21310,7 +21312,7 @@
       <c r="Y748" s="1"/>
       <c r="Z748" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="749">
+    <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -21338,7 +21340,7 @@
       <c r="Y749" s="1"/>
       <c r="Z749" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="750">
+    <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -21366,7 +21368,7 @@
       <c r="Y750" s="1"/>
       <c r="Z750" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="751">
+    <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -21394,7 +21396,7 @@
       <c r="Y751" s="1"/>
       <c r="Z751" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="752">
+    <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -21422,7 +21424,7 @@
       <c r="Y752" s="1"/>
       <c r="Z752" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="753">
+    <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -21450,7 +21452,7 @@
       <c r="Y753" s="1"/>
       <c r="Z753" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="754">
+    <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -21478,7 +21480,7 @@
       <c r="Y754" s="1"/>
       <c r="Z754" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="755">
+    <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -21506,7 +21508,7 @@
       <c r="Y755" s="1"/>
       <c r="Z755" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="756">
+    <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -21534,7 +21536,7 @@
       <c r="Y756" s="1"/>
       <c r="Z756" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="757">
+    <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -21562,7 +21564,7 @@
       <c r="Y757" s="1"/>
       <c r="Z757" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="758">
+    <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -21590,7 +21592,7 @@
       <c r="Y758" s="1"/>
       <c r="Z758" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="759">
+    <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -21618,7 +21620,7 @@
       <c r="Y759" s="1"/>
       <c r="Z759" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="760">
+    <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -21646,7 +21648,7 @@
       <c r="Y760" s="1"/>
       <c r="Z760" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="761">
+    <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -21674,7 +21676,7 @@
       <c r="Y761" s="1"/>
       <c r="Z761" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="762">
+    <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -21702,7 +21704,7 @@
       <c r="Y762" s="1"/>
       <c r="Z762" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="763">
+    <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -21730,7 +21732,7 @@
       <c r="Y763" s="1"/>
       <c r="Z763" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="764">
+    <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -21758,7 +21760,7 @@
       <c r="Y764" s="1"/>
       <c r="Z764" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="765">
+    <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -21786,7 +21788,7 @@
       <c r="Y765" s="1"/>
       <c r="Z765" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="766">
+    <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -21814,7 +21816,7 @@
       <c r="Y766" s="1"/>
       <c r="Z766" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="767">
+    <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -21842,7 +21844,7 @@
       <c r="Y767" s="1"/>
       <c r="Z767" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="768">
+    <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -21870,7 +21872,7 @@
       <c r="Y768" s="1"/>
       <c r="Z768" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="769">
+    <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -21898,7 +21900,7 @@
       <c r="Y769" s="1"/>
       <c r="Z769" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="770">
+    <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -21926,7 +21928,7 @@
       <c r="Y770" s="1"/>
       <c r="Z770" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="771">
+    <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -21954,7 +21956,7 @@
       <c r="Y771" s="1"/>
       <c r="Z771" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="772">
+    <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -21982,7 +21984,7 @@
       <c r="Y772" s="1"/>
       <c r="Z772" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="773">
+    <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -22010,7 +22012,7 @@
       <c r="Y773" s="1"/>
       <c r="Z773" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="774">
+    <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -22038,7 +22040,7 @@
       <c r="Y774" s="1"/>
       <c r="Z774" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="775">
+    <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -22066,7 +22068,7 @@
       <c r="Y775" s="1"/>
       <c r="Z775" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="776">
+    <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -22094,7 +22096,7 @@
       <c r="Y776" s="1"/>
       <c r="Z776" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="777">
+    <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -22122,7 +22124,7 @@
       <c r="Y777" s="1"/>
       <c r="Z777" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="778">
+    <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -22150,7 +22152,7 @@
       <c r="Y778" s="1"/>
       <c r="Z778" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="779">
+    <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -22178,7 +22180,7 @@
       <c r="Y779" s="1"/>
       <c r="Z779" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="780">
+    <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -22206,7 +22208,7 @@
       <c r="Y780" s="1"/>
       <c r="Z780" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="781">
+    <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -22234,7 +22236,7 @@
       <c r="Y781" s="1"/>
       <c r="Z781" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="782">
+    <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -22262,7 +22264,7 @@
       <c r="Y782" s="1"/>
       <c r="Z782" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="783">
+    <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -22290,7 +22292,7 @@
       <c r="Y783" s="1"/>
       <c r="Z783" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="784">
+    <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -22318,7 +22320,7 @@
       <c r="Y784" s="1"/>
       <c r="Z784" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="785">
+    <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -22346,7 +22348,7 @@
       <c r="Y785" s="1"/>
       <c r="Z785" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="786">
+    <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -22374,7 +22376,7 @@
       <c r="Y786" s="1"/>
       <c r="Z786" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="787">
+    <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -22402,7 +22404,7 @@
       <c r="Y787" s="1"/>
       <c r="Z787" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="788">
+    <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -22430,7 +22432,7 @@
       <c r="Y788" s="1"/>
       <c r="Z788" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="789">
+    <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -22458,7 +22460,7 @@
       <c r="Y789" s="1"/>
       <c r="Z789" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="790">
+    <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -22486,7 +22488,7 @@
       <c r="Y790" s="1"/>
       <c r="Z790" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="791">
+    <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -22514,7 +22516,7 @@
       <c r="Y791" s="1"/>
       <c r="Z791" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="792">
+    <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -22542,7 +22544,7 @@
       <c r="Y792" s="1"/>
       <c r="Z792" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="793">
+    <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -22570,7 +22572,7 @@
       <c r="Y793" s="1"/>
       <c r="Z793" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="794">
+    <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -22598,7 +22600,7 @@
       <c r="Y794" s="1"/>
       <c r="Z794" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="795">
+    <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -22626,7 +22628,7 @@
       <c r="Y795" s="1"/>
       <c r="Z795" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="796">
+    <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -22654,7 +22656,7 @@
       <c r="Y796" s="1"/>
       <c r="Z796" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="797">
+    <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -22682,7 +22684,7 @@
       <c r="Y797" s="1"/>
       <c r="Z797" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="798">
+    <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -22710,7 +22712,7 @@
       <c r="Y798" s="1"/>
       <c r="Z798" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="799">
+    <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -22738,7 +22740,7 @@
       <c r="Y799" s="1"/>
       <c r="Z799" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="800">
+    <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -22766,7 +22768,7 @@
       <c r="Y800" s="1"/>
       <c r="Z800" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="801">
+    <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -22794,7 +22796,7 @@
       <c r="Y801" s="1"/>
       <c r="Z801" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="802">
+    <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -22822,7 +22824,7 @@
       <c r="Y802" s="1"/>
       <c r="Z802" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="803">
+    <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -22850,7 +22852,7 @@
       <c r="Y803" s="1"/>
       <c r="Z803" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="804">
+    <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -22878,7 +22880,7 @@
       <c r="Y804" s="1"/>
       <c r="Z804" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="805">
+    <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -22906,7 +22908,7 @@
       <c r="Y805" s="1"/>
       <c r="Z805" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="806">
+    <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -22934,7 +22936,7 @@
       <c r="Y806" s="1"/>
       <c r="Z806" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="807">
+    <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -22962,7 +22964,7 @@
       <c r="Y807" s="1"/>
       <c r="Z807" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="808">
+    <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -22990,7 +22992,7 @@
       <c r="Y808" s="1"/>
       <c r="Z808" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="809">
+    <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -23018,7 +23020,7 @@
       <c r="Y809" s="1"/>
       <c r="Z809" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="810">
+    <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -23046,7 +23048,7 @@
       <c r="Y810" s="1"/>
       <c r="Z810" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="811">
+    <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -23074,7 +23076,7 @@
       <c r="Y811" s="1"/>
       <c r="Z811" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="812">
+    <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -23102,7 +23104,7 @@
       <c r="Y812" s="1"/>
       <c r="Z812" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="813">
+    <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -23130,7 +23132,7 @@
       <c r="Y813" s="1"/>
       <c r="Z813" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="814">
+    <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -23158,7 +23160,7 @@
       <c r="Y814" s="1"/>
       <c r="Z814" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="815">
+    <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -23186,7 +23188,7 @@
       <c r="Y815" s="1"/>
       <c r="Z815" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="816">
+    <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -23214,7 +23216,7 @@
       <c r="Y816" s="1"/>
       <c r="Z816" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="817">
+    <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -23242,7 +23244,7 @@
       <c r="Y817" s="1"/>
       <c r="Z817" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="818">
+    <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -23270,7 +23272,7 @@
       <c r="Y818" s="1"/>
       <c r="Z818" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="819">
+    <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -23298,7 +23300,7 @@
       <c r="Y819" s="1"/>
       <c r="Z819" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="820">
+    <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -23326,7 +23328,7 @@
       <c r="Y820" s="1"/>
       <c r="Z820" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="821">
+    <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -23354,7 +23356,7 @@
       <c r="Y821" s="1"/>
       <c r="Z821" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="822">
+    <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -23382,7 +23384,7 @@
       <c r="Y822" s="1"/>
       <c r="Z822" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="823">
+    <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -23410,7 +23412,7 @@
       <c r="Y823" s="1"/>
       <c r="Z823" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="824">
+    <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -23438,7 +23440,7 @@
       <c r="Y824" s="1"/>
       <c r="Z824" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="825">
+    <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -23466,7 +23468,7 @@
       <c r="Y825" s="1"/>
       <c r="Z825" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="826">
+    <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -23494,7 +23496,7 @@
       <c r="Y826" s="1"/>
       <c r="Z826" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="827">
+    <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -23522,7 +23524,7 @@
       <c r="Y827" s="1"/>
       <c r="Z827" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="828">
+    <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -23550,7 +23552,7 @@
       <c r="Y828" s="1"/>
       <c r="Z828" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="829">
+    <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -23578,7 +23580,7 @@
       <c r="Y829" s="1"/>
       <c r="Z829" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="830">
+    <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -23606,7 +23608,7 @@
       <c r="Y830" s="1"/>
       <c r="Z830" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="831">
+    <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -23634,7 +23636,7 @@
       <c r="Y831" s="1"/>
       <c r="Z831" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="832">
+    <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -23662,7 +23664,7 @@
       <c r="Y832" s="1"/>
       <c r="Z832" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="833">
+    <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -23690,7 +23692,7 @@
       <c r="Y833" s="1"/>
       <c r="Z833" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="834">
+    <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -23718,7 +23720,7 @@
       <c r="Y834" s="1"/>
       <c r="Z834" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="835">
+    <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -23746,7 +23748,7 @@
       <c r="Y835" s="1"/>
       <c r="Z835" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="836">
+    <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -23774,7 +23776,7 @@
       <c r="Y836" s="1"/>
       <c r="Z836" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="837">
+    <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -23802,7 +23804,7 @@
       <c r="Y837" s="1"/>
       <c r="Z837" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="838">
+    <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -23830,7 +23832,7 @@
       <c r="Y838" s="1"/>
       <c r="Z838" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="839">
+    <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -23858,7 +23860,7 @@
       <c r="Y839" s="1"/>
       <c r="Z839" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="840">
+    <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -23886,7 +23888,7 @@
       <c r="Y840" s="1"/>
       <c r="Z840" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="841">
+    <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -23914,7 +23916,7 @@
       <c r="Y841" s="1"/>
       <c r="Z841" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="842">
+    <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -23942,7 +23944,7 @@
       <c r="Y842" s="1"/>
       <c r="Z842" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="843">
+    <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -23970,7 +23972,7 @@
       <c r="Y843" s="1"/>
       <c r="Z843" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="844">
+    <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -23998,7 +24000,7 @@
       <c r="Y844" s="1"/>
       <c r="Z844" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="845">
+    <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -24026,7 +24028,7 @@
       <c r="Y845" s="1"/>
       <c r="Z845" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="846">
+    <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -24054,7 +24056,7 @@
       <c r="Y846" s="1"/>
       <c r="Z846" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="847">
+    <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -24082,7 +24084,7 @@
       <c r="Y847" s="1"/>
       <c r="Z847" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="848">
+    <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -24110,7 +24112,7 @@
       <c r="Y848" s="1"/>
       <c r="Z848" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="849">
+    <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -24138,7 +24140,7 @@
       <c r="Y849" s="1"/>
       <c r="Z849" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="850">
+    <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -24166,7 +24168,7 @@
       <c r="Y850" s="1"/>
       <c r="Z850" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="851">
+    <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -24194,7 +24196,7 @@
       <c r="Y851" s="1"/>
       <c r="Z851" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="852">
+    <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -24222,7 +24224,7 @@
       <c r="Y852" s="1"/>
       <c r="Z852" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="853">
+    <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -24250,7 +24252,7 @@
       <c r="Y853" s="1"/>
       <c r="Z853" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="854">
+    <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -24278,7 +24280,7 @@
       <c r="Y854" s="1"/>
       <c r="Z854" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="855">
+    <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -24306,7 +24308,7 @@
       <c r="Y855" s="1"/>
       <c r="Z855" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="856">
+    <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -24334,7 +24336,7 @@
       <c r="Y856" s="1"/>
       <c r="Z856" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="857">
+    <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -24362,7 +24364,7 @@
       <c r="Y857" s="1"/>
       <c r="Z857" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="858">
+    <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -24390,7 +24392,7 @@
       <c r="Y858" s="1"/>
       <c r="Z858" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="859">
+    <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -24418,7 +24420,7 @@
       <c r="Y859" s="1"/>
       <c r="Z859" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="860">
+    <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -24446,7 +24448,7 @@
       <c r="Y860" s="1"/>
       <c r="Z860" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="861">
+    <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -24474,7 +24476,7 @@
       <c r="Y861" s="1"/>
       <c r="Z861" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="862">
+    <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -24502,7 +24504,7 @@
       <c r="Y862" s="1"/>
       <c r="Z862" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="863">
+    <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -24530,7 +24532,7 @@
       <c r="Y863" s="1"/>
       <c r="Z863" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="864">
+    <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -24558,7 +24560,7 @@
       <c r="Y864" s="1"/>
       <c r="Z864" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="865">
+    <row r="865" ht="15.75" customHeight="1">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -24586,7 +24588,7 @@
       <c r="Y865" s="1"/>
       <c r="Z865" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="866">
+    <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -24614,7 +24616,7 @@
       <c r="Y866" s="1"/>
       <c r="Z866" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="867">
+    <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -24642,7 +24644,7 @@
       <c r="Y867" s="1"/>
       <c r="Z867" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="868">
+    <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -24670,7 +24672,7 @@
       <c r="Y868" s="1"/>
       <c r="Z868" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="869">
+    <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -24698,7 +24700,7 @@
       <c r="Y869" s="1"/>
       <c r="Z869" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="870">
+    <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -24726,7 +24728,7 @@
       <c r="Y870" s="1"/>
       <c r="Z870" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="871">
+    <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -24754,7 +24756,7 @@
       <c r="Y871" s="1"/>
       <c r="Z871" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="872">
+    <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -24782,7 +24784,7 @@
       <c r="Y872" s="1"/>
       <c r="Z872" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="873">
+    <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -24810,7 +24812,7 @@
       <c r="Y873" s="1"/>
       <c r="Z873" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="874">
+    <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -24838,7 +24840,7 @@
       <c r="Y874" s="1"/>
       <c r="Z874" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="875">
+    <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -24866,7 +24868,7 @@
       <c r="Y875" s="1"/>
       <c r="Z875" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="876">
+    <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -24894,7 +24896,7 @@
       <c r="Y876" s="1"/>
       <c r="Z876" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="877">
+    <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -24922,7 +24924,7 @@
       <c r="Y877" s="1"/>
       <c r="Z877" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="878">
+    <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -24950,7 +24952,7 @@
       <c r="Y878" s="1"/>
       <c r="Z878" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="879">
+    <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -24978,7 +24980,7 @@
       <c r="Y879" s="1"/>
       <c r="Z879" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="880">
+    <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -25006,7 +25008,7 @@
       <c r="Y880" s="1"/>
       <c r="Z880" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="881">
+    <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -25034,7 +25036,7 @@
       <c r="Y881" s="1"/>
       <c r="Z881" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="882">
+    <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -25062,7 +25064,7 @@
       <c r="Y882" s="1"/>
       <c r="Z882" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="883">
+    <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -25090,7 +25092,7 @@
       <c r="Y883" s="1"/>
       <c r="Z883" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="884">
+    <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -25118,7 +25120,7 @@
       <c r="Y884" s="1"/>
       <c r="Z884" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="885">
+    <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -25146,7 +25148,7 @@
       <c r="Y885" s="1"/>
       <c r="Z885" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="886">
+    <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -25174,7 +25176,7 @@
       <c r="Y886" s="1"/>
       <c r="Z886" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="887">
+    <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -25202,7 +25204,7 @@
       <c r="Y887" s="1"/>
       <c r="Z887" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="888">
+    <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -25230,7 +25232,7 @@
       <c r="Y888" s="1"/>
       <c r="Z888" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="889">
+    <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -25258,7 +25260,7 @@
       <c r="Y889" s="1"/>
       <c r="Z889" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="890">
+    <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -25286,7 +25288,7 @@
       <c r="Y890" s="1"/>
       <c r="Z890" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="891">
+    <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -25314,7 +25316,7 @@
       <c r="Y891" s="1"/>
       <c r="Z891" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="892">
+    <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -25342,7 +25344,7 @@
       <c r="Y892" s="1"/>
       <c r="Z892" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="893">
+    <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -25370,7 +25372,7 @@
       <c r="Y893" s="1"/>
       <c r="Z893" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="894">
+    <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -25398,7 +25400,7 @@
       <c r="Y894" s="1"/>
       <c r="Z894" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="895">
+    <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -25426,7 +25428,7 @@
       <c r="Y895" s="1"/>
       <c r="Z895" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="896">
+    <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -25454,7 +25456,7 @@
       <c r="Y896" s="1"/>
       <c r="Z896" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="897">
+    <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -25482,7 +25484,7 @@
       <c r="Y897" s="1"/>
       <c r="Z897" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="898">
+    <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -25510,7 +25512,7 @@
       <c r="Y898" s="1"/>
       <c r="Z898" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="899">
+    <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -25538,7 +25540,7 @@
       <c r="Y899" s="1"/>
       <c r="Z899" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="900">
+    <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -25566,7 +25568,7 @@
       <c r="Y900" s="1"/>
       <c r="Z900" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="901">
+    <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -25594,7 +25596,7 @@
       <c r="Y901" s="1"/>
       <c r="Z901" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="902">
+    <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -25622,7 +25624,7 @@
       <c r="Y902" s="1"/>
       <c r="Z902" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="903">
+    <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -25650,7 +25652,7 @@
       <c r="Y903" s="1"/>
       <c r="Z903" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="904">
+    <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -25678,7 +25680,7 @@
       <c r="Y904" s="1"/>
       <c r="Z904" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="905">
+    <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -25706,7 +25708,7 @@
       <c r="Y905" s="1"/>
       <c r="Z905" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="906">
+    <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -25734,7 +25736,7 @@
       <c r="Y906" s="1"/>
       <c r="Z906" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="907">
+    <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -25762,7 +25764,7 @@
       <c r="Y907" s="1"/>
       <c r="Z907" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="908">
+    <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -25790,7 +25792,7 @@
       <c r="Y908" s="1"/>
       <c r="Z908" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="909">
+    <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -25818,7 +25820,7 @@
       <c r="Y909" s="1"/>
       <c r="Z909" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="910">
+    <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -25846,7 +25848,7 @@
       <c r="Y910" s="1"/>
       <c r="Z910" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="911">
+    <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -25874,7 +25876,7 @@
       <c r="Y911" s="1"/>
       <c r="Z911" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="912">
+    <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -25902,7 +25904,7 @@
       <c r="Y912" s="1"/>
       <c r="Z912" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="913">
+    <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -25930,7 +25932,7 @@
       <c r="Y913" s="1"/>
       <c r="Z913" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="914">
+    <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -25958,7 +25960,7 @@
       <c r="Y914" s="1"/>
       <c r="Z914" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="915">
+    <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -25986,7 +25988,7 @@
       <c r="Y915" s="1"/>
       <c r="Z915" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="916">
+    <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -26014,7 +26016,7 @@
       <c r="Y916" s="1"/>
       <c r="Z916" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="917">
+    <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -26042,7 +26044,7 @@
       <c r="Y917" s="1"/>
       <c r="Z917" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="918">
+    <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -26070,7 +26072,7 @@
       <c r="Y918" s="1"/>
       <c r="Z918" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="919">
+    <row r="919" ht="15.75" customHeight="1">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -26098,7 +26100,7 @@
       <c r="Y919" s="1"/>
       <c r="Z919" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="920">
+    <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -26126,7 +26128,7 @@
       <c r="Y920" s="1"/>
       <c r="Z920" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="921">
+    <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -26154,7 +26156,7 @@
       <c r="Y921" s="1"/>
       <c r="Z921" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="922">
+    <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -26182,7 +26184,7 @@
       <c r="Y922" s="1"/>
       <c r="Z922" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="923">
+    <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -26210,7 +26212,7 @@
       <c r="Y923" s="1"/>
       <c r="Z923" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="924">
+    <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -26238,7 +26240,7 @@
       <c r="Y924" s="1"/>
       <c r="Z924" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="925">
+    <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -26266,7 +26268,7 @@
       <c r="Y925" s="1"/>
       <c r="Z925" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="926">
+    <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -26294,7 +26296,7 @@
       <c r="Y926" s="1"/>
       <c r="Z926" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="927">
+    <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -26322,7 +26324,7 @@
       <c r="Y927" s="1"/>
       <c r="Z927" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="928">
+    <row r="928" ht="15.75" customHeight="1">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -26350,7 +26352,7 @@
       <c r="Y928" s="1"/>
       <c r="Z928" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="929">
+    <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -26378,7 +26380,7 @@
       <c r="Y929" s="1"/>
       <c r="Z929" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="930">
+    <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -26406,7 +26408,7 @@
       <c r="Y930" s="1"/>
       <c r="Z930" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="931">
+    <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -26434,7 +26436,7 @@
       <c r="Y931" s="1"/>
       <c r="Z931" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="932">
+    <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -26462,7 +26464,7 @@
       <c r="Y932" s="1"/>
       <c r="Z932" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="933">
+    <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -26490,7 +26492,7 @@
       <c r="Y933" s="1"/>
       <c r="Z933" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="934">
+    <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -26518,7 +26520,7 @@
       <c r="Y934" s="1"/>
       <c r="Z934" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="935">
+    <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -26546,7 +26548,7 @@
       <c r="Y935" s="1"/>
       <c r="Z935" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="936">
+    <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -26574,7 +26576,7 @@
       <c r="Y936" s="1"/>
       <c r="Z936" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="937">
+    <row r="937" ht="15.75" customHeight="1">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -26602,7 +26604,7 @@
       <c r="Y937" s="1"/>
       <c r="Z937" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="938">
+    <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -26630,7 +26632,7 @@
       <c r="Y938" s="1"/>
       <c r="Z938" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="939">
+    <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -26658,7 +26660,7 @@
       <c r="Y939" s="1"/>
       <c r="Z939" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="940">
+    <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -26686,7 +26688,7 @@
       <c r="Y940" s="1"/>
       <c r="Z940" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="941">
+    <row r="941" ht="15.75" customHeight="1">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -26714,7 +26716,7 @@
       <c r="Y941" s="1"/>
       <c r="Z941" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="942">
+    <row r="942" ht="15.75" customHeight="1">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -26742,7 +26744,7 @@
       <c r="Y942" s="1"/>
       <c r="Z942" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="943">
+    <row r="943" ht="15.75" customHeight="1">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -26770,7 +26772,7 @@
       <c r="Y943" s="1"/>
       <c r="Z943" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="944">
+    <row r="944" ht="15.75" customHeight="1">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -26798,7 +26800,7 @@
       <c r="Y944" s="1"/>
       <c r="Z944" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="945">
+    <row r="945" ht="15.75" customHeight="1">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -26826,7 +26828,7 @@
       <c r="Y945" s="1"/>
       <c r="Z945" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="946">
+    <row r="946" ht="15.75" customHeight="1">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -26854,7 +26856,7 @@
       <c r="Y946" s="1"/>
       <c r="Z946" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="947">
+    <row r="947" ht="15.75" customHeight="1">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -26882,7 +26884,7 @@
       <c r="Y947" s="1"/>
       <c r="Z947" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="948">
+    <row r="948" ht="15.75" customHeight="1">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -26910,7 +26912,7 @@
       <c r="Y948" s="1"/>
       <c r="Z948" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="949">
+    <row r="949" ht="15.75" customHeight="1">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -26938,7 +26940,7 @@
       <c r="Y949" s="1"/>
       <c r="Z949" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="950">
+    <row r="950" ht="15.75" customHeight="1">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -26966,7 +26968,7 @@
       <c r="Y950" s="1"/>
       <c r="Z950" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="951">
+    <row r="951" ht="15.75" customHeight="1">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -26994,7 +26996,7 @@
       <c r="Y951" s="1"/>
       <c r="Z951" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="952">
+    <row r="952" ht="15.75" customHeight="1">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -27022,7 +27024,7 @@
       <c r="Y952" s="1"/>
       <c r="Z952" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="953">
+    <row r="953" ht="15.75" customHeight="1">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -27050,7 +27052,7 @@
       <c r="Y953" s="1"/>
       <c r="Z953" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="954">
+    <row r="954" ht="15.75" customHeight="1">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -27078,7 +27080,7 @@
       <c r="Y954" s="1"/>
       <c r="Z954" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="955">
+    <row r="955" ht="15.75" customHeight="1">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -27106,7 +27108,7 @@
       <c r="Y955" s="1"/>
       <c r="Z955" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="956">
+    <row r="956" ht="15.75" customHeight="1">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -27134,7 +27136,7 @@
       <c r="Y956" s="1"/>
       <c r="Z956" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="957">
+    <row r="957" ht="15.75" customHeight="1">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -27162,7 +27164,7 @@
       <c r="Y957" s="1"/>
       <c r="Z957" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="958">
+    <row r="958" ht="15.75" customHeight="1">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -27190,7 +27192,7 @@
       <c r="Y958" s="1"/>
       <c r="Z958" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="959">
+    <row r="959" ht="15.75" customHeight="1">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -27218,7 +27220,7 @@
       <c r="Y959" s="1"/>
       <c r="Z959" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="960">
+    <row r="960" ht="15.75" customHeight="1">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -27246,7 +27248,7 @@
       <c r="Y960" s="1"/>
       <c r="Z960" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="961">
+    <row r="961" ht="15.75" customHeight="1">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -27274,7 +27276,7 @@
       <c r="Y961" s="1"/>
       <c r="Z961" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="962">
+    <row r="962" ht="15.75" customHeight="1">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -27302,7 +27304,7 @@
       <c r="Y962" s="1"/>
       <c r="Z962" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="963">
+    <row r="963" ht="15.75" customHeight="1">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -27330,7 +27332,7 @@
       <c r="Y963" s="1"/>
       <c r="Z963" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="964">
+    <row r="964" ht="15.75" customHeight="1">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -27358,7 +27360,7 @@
       <c r="Y964" s="1"/>
       <c r="Z964" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="965">
+    <row r="965" ht="15.75" customHeight="1">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -27386,7 +27388,7 @@
       <c r="Y965" s="1"/>
       <c r="Z965" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="966">
+    <row r="966" ht="15.75" customHeight="1">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -27414,7 +27416,7 @@
       <c r="Y966" s="1"/>
       <c r="Z966" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="967">
+    <row r="967" ht="15.75" customHeight="1">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -27442,7 +27444,7 @@
       <c r="Y967" s="1"/>
       <c r="Z967" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="968">
+    <row r="968" ht="15.75" customHeight="1">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -27470,7 +27472,7 @@
       <c r="Y968" s="1"/>
       <c r="Z968" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="969">
+    <row r="969" ht="15.75" customHeight="1">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -27498,7 +27500,7 @@
       <c r="Y969" s="1"/>
       <c r="Z969" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="970">
+    <row r="970" ht="15.75" customHeight="1">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -27526,7 +27528,7 @@
       <c r="Y970" s="1"/>
       <c r="Z970" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="971">
+    <row r="971" ht="15.75" customHeight="1">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -27554,7 +27556,7 @@
       <c r="Y971" s="1"/>
       <c r="Z971" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="972">
+    <row r="972" ht="15.75" customHeight="1">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -27582,7 +27584,7 @@
       <c r="Y972" s="1"/>
       <c r="Z972" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="973">
+    <row r="973" ht="15.75" customHeight="1">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -27610,7 +27612,7 @@
       <c r="Y973" s="1"/>
       <c r="Z973" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="974">
+    <row r="974" ht="15.75" customHeight="1">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -27638,7 +27640,7 @@
       <c r="Y974" s="1"/>
       <c r="Z974" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="975">
+    <row r="975" ht="15.75" customHeight="1">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -27666,7 +27668,7 @@
       <c r="Y975" s="1"/>
       <c r="Z975" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="976">
+    <row r="976" ht="15.75" customHeight="1">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -27694,7 +27696,7 @@
       <c r="Y976" s="1"/>
       <c r="Z976" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="977">
+    <row r="977" ht="15.75" customHeight="1">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -27722,7 +27724,7 @@
       <c r="Y977" s="1"/>
       <c r="Z977" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="978">
+    <row r="978" ht="15.75" customHeight="1">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -27750,7 +27752,7 @@
       <c r="Y978" s="1"/>
       <c r="Z978" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="979">
+    <row r="979" ht="15.75" customHeight="1">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -27778,7 +27780,7 @@
       <c r="Y979" s="1"/>
       <c r="Z979" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="980">
+    <row r="980" ht="15.75" customHeight="1">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -27806,7 +27808,7 @@
       <c r="Y980" s="1"/>
       <c r="Z980" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="981">
+    <row r="981" ht="15.75" customHeight="1">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -27834,7 +27836,7 @@
       <c r="Y981" s="1"/>
       <c r="Z981" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="982">
+    <row r="982" ht="15.75" customHeight="1">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -27862,7 +27864,7 @@
       <c r="Y982" s="1"/>
       <c r="Z982" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="983">
+    <row r="983" ht="15.75" customHeight="1">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -27890,7 +27892,7 @@
       <c r="Y983" s="1"/>
       <c r="Z983" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="984">
+    <row r="984" ht="15.75" customHeight="1">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -27918,7 +27920,7 @@
       <c r="Y984" s="1"/>
       <c r="Z984" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="985">
+    <row r="985" ht="15.75" customHeight="1">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -27946,7 +27948,7 @@
       <c r="Y985" s="1"/>
       <c r="Z985" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="986">
+    <row r="986" ht="15.75" customHeight="1">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -27974,7 +27976,7 @@
       <c r="Y986" s="1"/>
       <c r="Z986" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="987">
+    <row r="987" ht="15.75" customHeight="1">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -28002,7 +28004,7 @@
       <c r="Y987" s="1"/>
       <c r="Z987" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="988">
+    <row r="988" ht="15.75" customHeight="1">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -28030,7 +28032,7 @@
       <c r="Y988" s="1"/>
       <c r="Z988" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="989">
+    <row r="989" ht="15.75" customHeight="1">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -28058,7 +28060,7 @@
       <c r="Y989" s="1"/>
       <c r="Z989" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="990">
+    <row r="990" ht="15.75" customHeight="1">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -28086,7 +28088,7 @@
       <c r="Y990" s="1"/>
       <c r="Z990" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="991">
+    <row r="991" ht="15.75" customHeight="1">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -28114,7 +28116,7 @@
       <c r="Y991" s="1"/>
       <c r="Z991" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="992">
+    <row r="992" ht="15.75" customHeight="1">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -28142,7 +28144,7 @@
       <c r="Y992" s="1"/>
       <c r="Z992" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="993">
+    <row r="993" ht="15.75" customHeight="1">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -28170,7 +28172,7 @@
       <c r="Y993" s="1"/>
       <c r="Z993" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="994">
+    <row r="994" ht="15.75" customHeight="1">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -28198,7 +28200,7 @@
       <c r="Y994" s="1"/>
       <c r="Z994" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="995">
+    <row r="995" ht="15.75" customHeight="1">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -28226,7 +28228,7 @@
       <c r="Y995" s="1"/>
       <c r="Z995" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="996">
+    <row r="996" ht="15.75" customHeight="1">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -28254,7 +28256,7 @@
       <c r="Y996" s="1"/>
       <c r="Z996" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="997">
+    <row r="997" ht="15.75" customHeight="1">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -28282,7 +28284,7 @@
       <c r="Y997" s="1"/>
       <c r="Z997" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="998">
+    <row r="998" ht="15.75" customHeight="1">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -28310,7 +28312,7 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="999">
+    <row r="999" ht="15.75" customHeight="1">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -28338,7 +28340,7 @@
       <c r="Y999" s="1"/>
       <c r="Z999" s="1"/>
     </row>
-    <row ht="15.75" customHeight="1" r="1000">
+    <row r="1000" ht="15.75" customHeight="1">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -28372,16 +28374,266 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="37.53" customWidth="1"/>
-    <col min="3" max="3" width="19.56" customWidth="1"/>
-    <col min="4" max="4" width="19.71" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="14.89"/>
+    <col customWidth="1" min="3" max="3" width="18.22"/>
+    <col customWidth="1" min="4" max="4" width="15.22"/>
+    <col customWidth="1" min="5" max="5" width="30.22"/>
   </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46154.72222222222</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46154.76388888889</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46161.72222222222</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46161.76388888889</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46168.72222222222</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46168.76388888889</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46149.708333333336</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46149.75</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46156.729166666664</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46156.770833333336</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46163.708333333336</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46163.75</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46170.708333333336</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46170.75</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46155.708333333336</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46155.75</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4">
+        <v>46162.708333333336</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46162.739583333336</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4">
+        <v>46162.739583333336</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46162.770833333336</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
+        <v>46169.708333333336</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46169.75</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4">
+        <v>46150.666666666664</v>
+      </c>
+      <c r="D13" s="4">
+        <v>46150.70138888889</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4">
+        <v>46157.666666666664</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46157.70138888889</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4">
+        <v>46164.666666666664</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46164.70138888889</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="4">
+        <v>46171.666666666664</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46171.70138888889</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -28397,64 +28649,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="18.59" customWidth="1"/>
-    <col min="4" max="4" width="19.12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/events.xlsx
+++ b/events.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="21">
   <si>
     <t>description</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>通町コミュニティセンター 大広間</t>
+  </si>
+  <si>
+    <t>夏祭り</t>
+  </si>
+  <si>
+    <t>小学校</t>
   </si>
 </sst>
 </file>
@@ -28649,6 +28655,20 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46259.666666666664</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46259.833333333336</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/events.xlsx
+++ b/events.xlsx
@@ -1,7 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="2"/>
+  </bookViews>
   <sheets>
     <sheet state="visible" name="club" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Karate" sheetId="2" r:id="rId6"/>
@@ -82,25 +85,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1" mc:Ignorable="x14ac">
+  <numFmts count="9">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);(&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);(&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red](&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* (#,##0.00);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* (#,##0.00);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="12.0"/>
+      <name val="Calibri"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <name val="Times New Roman"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
+      <sz val="12"/>
     </font>
     <font>
-      <color theme="1"/>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -116,25 +128,17 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
@@ -351,17 +355,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.89"/>
-    <col customWidth="1" min="2" max="2" width="13.11"/>
-    <col customWidth="1" min="3" max="3" width="17.22"/>
-    <col customWidth="1" min="4" max="4" width="21.0"/>
+    <col min="1" max="1" width="11.89" customWidth="1"/>
+    <col min="2" max="2" width="13.11" customWidth="1"/>
+    <col min="3" max="3" width="17.22" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -371,7 +377,9 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -934,7 +942,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -962,7 +970,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -990,7 +998,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1018,7 +1026,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1046,7 +1054,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1074,7 +1082,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1102,7 +1110,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1130,7 +1138,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1158,7 +1166,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1186,7 +1194,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1214,7 +1222,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1242,7 +1250,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1270,7 +1278,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1298,7 +1306,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1326,7 +1334,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1354,7 +1362,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1382,7 +1390,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1410,7 +1418,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1438,7 +1446,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1466,7 +1474,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1494,7 +1502,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1522,7 +1530,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1550,7 +1558,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1578,7 +1586,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1606,7 +1614,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1634,7 +1642,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1662,7 +1670,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1690,7 +1698,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1718,7 +1726,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1746,7 +1754,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="50">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1774,7 +1782,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="51">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1802,7 +1810,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="52">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1830,7 +1838,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="53">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1858,7 +1866,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="54">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1886,7 +1894,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="55">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1914,7 +1922,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="56">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1942,7 +1950,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="57">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1970,7 +1978,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="58">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1998,7 +2006,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="59">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2026,7 +2034,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="60">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2054,7 +2062,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="61">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2082,7 +2090,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="62">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2110,7 +2118,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="63">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2138,7 +2146,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="64">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2166,7 +2174,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="65">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2194,7 +2202,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="66">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2222,7 +2230,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="67">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2250,7 +2258,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="68">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2278,7 +2286,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="69">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2306,7 +2314,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="70">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2334,7 +2342,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="71">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2362,7 +2370,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="72">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2390,7 +2398,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="73">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2418,7 +2426,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="74">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2446,7 +2454,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="75">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2474,7 +2482,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="76">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2502,7 +2510,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="77">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2530,7 +2538,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="78">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2558,7 +2566,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="79">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2586,7 +2594,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="80">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2614,7 +2622,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="81">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2642,7 +2650,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="82">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2670,7 +2678,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="83">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -2698,7 +2706,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="84">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2726,7 +2734,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="85">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2754,7 +2762,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="86">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2782,7 +2790,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="87">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2810,7 +2818,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="88">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2838,7 +2846,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="89">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2866,7 +2874,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="90">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2894,7 +2902,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="91">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2922,7 +2930,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="92">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2950,7 +2958,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="93">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2978,7 +2986,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="94">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3006,7 +3014,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="95">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3034,7 +3042,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="96">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3062,7 +3070,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="97">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3090,7 +3098,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="98">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3118,7 +3126,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="99">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3146,7 +3154,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="100">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3174,7 +3182,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="101">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3202,7 +3210,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="102">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3230,7 +3238,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="103">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3258,7 +3266,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="104">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3286,7 +3294,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="105">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3314,7 +3322,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="106">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3342,7 +3350,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="107">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3370,7 +3378,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="108">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3398,7 +3406,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="109">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3426,7 +3434,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="110">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3454,7 +3462,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="111">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3482,7 +3490,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="112">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3510,7 +3518,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="113">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3538,7 +3546,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="114">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3566,7 +3574,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="115">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3594,7 +3602,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="116">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3622,7 +3630,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="117">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3650,7 +3658,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="118">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3678,7 +3686,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="119">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3706,7 +3714,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="120">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3734,7 +3742,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="121">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3762,7 +3770,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="122">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3790,7 +3798,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="123">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3818,7 +3826,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="124">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3846,7 +3854,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="125">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3874,7 +3882,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="126">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3902,7 +3910,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="127">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3930,7 +3938,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="128">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3958,7 +3966,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="129">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3986,7 +3994,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="130">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4014,7 +4022,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="131">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4042,7 +4050,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="132">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4070,7 +4078,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="133">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4098,7 +4106,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="134">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4126,7 +4134,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="135">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4154,7 +4162,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="136">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4182,7 +4190,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="137">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4210,7 +4218,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="138">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4238,7 +4246,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="139">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4266,7 +4274,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="140">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4294,7 +4302,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="141">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4322,7 +4330,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="142">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4350,7 +4358,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="143">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4378,7 +4386,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="144">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4406,7 +4414,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="145">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4434,7 +4442,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="146">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4462,7 +4470,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="147">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4490,7 +4498,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="148">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4518,7 +4526,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="149">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4546,7 +4554,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="150">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4574,7 +4582,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="151">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4602,7 +4610,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="152">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4630,7 +4638,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="153">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4658,7 +4666,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="154">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4686,7 +4694,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="155">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4714,7 +4722,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="156">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4742,7 +4750,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="157">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4770,7 +4778,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="158">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4798,7 +4806,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="159">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4826,7 +4834,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="160">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4854,7 +4862,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="161">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4882,7 +4890,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="162">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4910,7 +4918,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="163">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4938,7 +4946,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="164">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4966,7 +4974,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="165">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4994,7 +5002,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="166">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5022,7 +5030,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="167">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5050,7 +5058,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="168">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5078,7 +5086,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="169">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5106,7 +5114,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="170">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5134,7 +5142,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="171">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5162,7 +5170,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="172">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5190,7 +5198,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="173">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5218,7 +5226,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="174">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5246,7 +5254,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="175">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5274,7 +5282,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="176">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5302,7 +5310,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="177">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5330,7 +5338,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="178">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5358,7 +5366,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="179">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5386,7 +5394,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="180">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5414,7 +5422,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="181">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5442,7 +5450,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="182">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5470,7 +5478,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="183">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5498,7 +5506,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="184">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5526,7 +5534,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="185">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5554,7 +5562,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="186">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5582,7 +5590,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="187">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5610,7 +5618,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="188">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5638,7 +5646,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="189">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5666,7 +5674,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="190">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5694,7 +5702,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="191">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5722,7 +5730,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="192">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5750,7 +5758,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="193">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5778,7 +5786,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="194">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -5806,7 +5814,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="195">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -5834,7 +5842,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="196">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -5862,7 +5870,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="197">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -5890,7 +5898,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="198">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -5918,7 +5926,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="199">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -5946,7 +5954,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="200">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -5974,7 +5982,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="201">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6002,7 +6010,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="202">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6030,7 +6038,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="203">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6058,7 +6066,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="204">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6086,7 +6094,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="205">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6114,7 +6122,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="206">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6142,7 +6150,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="207">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6170,7 +6178,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="208">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6198,7 +6206,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="209">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6226,7 +6234,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="210">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6254,7 +6262,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="211">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6282,7 +6290,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="212">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6310,7 +6318,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="213">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6338,7 +6346,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="214">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6366,7 +6374,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="215">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6394,7 +6402,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="216">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6422,7 +6430,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="217">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6450,7 +6458,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="218">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6478,7 +6486,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="219">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6506,7 +6514,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="220">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6534,7 +6542,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="221">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6562,7 +6570,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="222">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6590,7 +6598,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="223">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6618,7 +6626,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="224">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6646,7 +6654,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="225">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6674,7 +6682,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="226">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6702,7 +6710,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="227">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6730,7 +6738,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="228">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -6758,7 +6766,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="229">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -6786,7 +6794,7 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="230">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -6814,7 +6822,7 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="231">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -6842,7 +6850,7 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="232">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -6870,7 +6878,7 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="233">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -6898,7 +6906,7 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="234">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -6926,7 +6934,7 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="235">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -6954,7 +6962,7 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="236">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -6982,7 +6990,7 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="237">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -7010,7 +7018,7 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="238">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -7038,7 +7046,7 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="239">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -7066,7 +7074,7 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="240">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7094,7 +7102,7 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="241">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7122,7 +7130,7 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="242">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7150,7 +7158,7 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="243">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7178,7 +7186,7 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="244">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -7206,7 +7214,7 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="245">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -7234,7 +7242,7 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="246">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -7262,7 +7270,7 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="247">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -7290,7 +7298,7 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="248">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -7318,7 +7326,7 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="249">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -7346,7 +7354,7 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="250">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -7374,7 +7382,7 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="251">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -7402,7 +7410,7 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="252">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -7430,7 +7438,7 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="253">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -7458,7 +7466,7 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="254">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -7486,7 +7494,7 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="255">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -7514,7 +7522,7 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="256">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -7542,7 +7550,7 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="257">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -7570,7 +7578,7 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="258">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -7598,7 +7606,7 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="259">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -7626,7 +7634,7 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="260">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -7654,7 +7662,7 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="261">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -7682,7 +7690,7 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="262">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -7710,7 +7718,7 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="263">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -7738,7 +7746,7 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="264">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -7766,7 +7774,7 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="265">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -7794,7 +7802,7 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="266">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -7822,7 +7830,7 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="267">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -7850,7 +7858,7 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="268">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -7878,7 +7886,7 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="269">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -7906,7 +7914,7 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="270">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -7934,7 +7942,7 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="271">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -7962,7 +7970,7 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="272">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -7990,7 +7998,7 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="273">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -8018,7 +8026,7 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="274">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -8046,7 +8054,7 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="275">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -8074,7 +8082,7 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="276">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -8102,7 +8110,7 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="277">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -8130,7 +8138,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="278">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -8158,7 +8166,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="279">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -8186,7 +8194,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="280">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -8214,7 +8222,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="281">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -8242,7 +8250,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="282">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -8270,7 +8278,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="283">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -8298,7 +8306,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="284">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -8326,7 +8334,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="285">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -8354,7 +8362,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="286">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -8382,7 +8390,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="287">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -8410,7 +8418,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="288">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -8438,7 +8446,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="289">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -8466,7 +8474,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="290">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -8494,7 +8502,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="291">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -8522,7 +8530,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="292">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -8550,7 +8558,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="293">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -8578,7 +8586,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="294">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -8606,7 +8614,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="295">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -8634,7 +8642,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="296">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -8662,7 +8670,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="297">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -8690,7 +8698,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="298">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -8718,7 +8726,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="299">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -8746,7 +8754,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="300">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -8774,7 +8782,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="301">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -8802,7 +8810,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="302">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -8830,7 +8838,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="303">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -8858,7 +8866,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="304">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -8886,7 +8894,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="305">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -8914,7 +8922,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="306">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -8942,7 +8950,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="307">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -8970,7 +8978,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="308">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -8998,7 +9006,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="309">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -9026,7 +9034,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="310">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -9054,7 +9062,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="311">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -9082,7 +9090,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="312">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -9110,7 +9118,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="313">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -9138,7 +9146,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="314">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -9166,7 +9174,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="315">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -9194,7 +9202,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="316">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -9222,7 +9230,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="317">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -9250,7 +9258,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="318">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -9278,7 +9286,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="319">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -9306,7 +9314,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="320">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -9334,7 +9342,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="321">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -9362,7 +9370,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="322">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -9390,7 +9398,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="323">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -9418,7 +9426,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="324">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -9446,7 +9454,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="325">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -9474,7 +9482,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="326">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -9502,7 +9510,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="327">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -9530,7 +9538,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="328">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -9558,7 +9566,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="329">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -9586,7 +9594,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="330">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -9614,7 +9622,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="331">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -9642,7 +9650,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="332">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -9670,7 +9678,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="333">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -9698,7 +9706,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="334">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -9726,7 +9734,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="335">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -9754,7 +9762,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="336">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -9782,7 +9790,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="337">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -9810,7 +9818,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="338">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -9838,7 +9846,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="339">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -9866,7 +9874,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="340">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -9894,7 +9902,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="341">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -9922,7 +9930,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="342">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -9950,7 +9958,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="343">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -9978,7 +9986,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="344">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -10006,7 +10014,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="345">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -10034,7 +10042,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="346">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -10062,7 +10070,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="347">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -10090,7 +10098,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="348">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -10118,7 +10126,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="349">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -10146,7 +10154,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="350">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -10174,7 +10182,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="351">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -10202,7 +10210,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="352">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -10230,7 +10238,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="353">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -10258,7 +10266,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="354">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -10286,7 +10294,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="355">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -10314,7 +10322,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="356">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -10342,7 +10350,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="357">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -10370,7 +10378,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="358">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -10398,7 +10406,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="359">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -10426,7 +10434,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="360">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -10454,7 +10462,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="361">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -10482,7 +10490,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="362">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -10510,7 +10518,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="363">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -10538,7 +10546,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="364">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -10566,7 +10574,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="365">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -10594,7 +10602,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="366">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -10622,7 +10630,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="367">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -10650,7 +10658,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="368">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -10678,7 +10686,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="369">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -10706,7 +10714,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="370">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -10734,7 +10742,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="371">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -10762,7 +10770,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="372">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -10790,7 +10798,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="373">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -10818,7 +10826,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="374">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -10846,7 +10854,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="375">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -10874,7 +10882,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="376">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -10902,7 +10910,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="377">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -10930,7 +10938,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="378">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -10958,7 +10966,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="379">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -10986,7 +10994,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="380">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -11014,7 +11022,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="381">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -11042,7 +11050,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="382">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -11070,7 +11078,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="383">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -11098,7 +11106,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="384">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -11126,7 +11134,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="385">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -11154,7 +11162,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="386">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -11182,7 +11190,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="387">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -11210,7 +11218,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="388">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -11238,7 +11246,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="389">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -11266,7 +11274,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="390">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -11294,7 +11302,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="391">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -11322,7 +11330,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="392">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -11350,7 +11358,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="393">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -11378,7 +11386,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="394">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -11406,7 +11414,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="395">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -11434,7 +11442,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="396">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -11462,7 +11470,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="397">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -11490,7 +11498,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="398">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -11518,7 +11526,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="399">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -11546,7 +11554,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="400">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -11574,7 +11582,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="401">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -11602,7 +11610,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="402">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -11630,7 +11638,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="403">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -11658,7 +11666,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="404">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -11686,7 +11694,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="405">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -11714,7 +11722,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="406">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -11742,7 +11750,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="407">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -11770,7 +11778,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="408">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -11798,7 +11806,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="409">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -11826,7 +11834,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="410">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -11854,7 +11862,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="411">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -11882,7 +11890,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="412">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -11910,7 +11918,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="413">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -11938,7 +11946,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="414">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -11966,7 +11974,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="415">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -11994,7 +12002,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="416">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -12022,7 +12030,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="417">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -12050,7 +12058,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="418">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -12078,7 +12086,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="419">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -12106,7 +12114,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="420">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -12134,7 +12142,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="421">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -12162,7 +12170,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="422">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -12190,7 +12198,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="423">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -12218,7 +12226,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="424">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -12246,7 +12254,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="425">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -12274,7 +12282,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="426">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -12302,7 +12310,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="427">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -12330,7 +12338,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="428">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -12358,7 +12366,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="429">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -12386,7 +12394,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="430">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -12414,7 +12422,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="431">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -12442,7 +12450,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="432">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -12470,7 +12478,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="433">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -12498,7 +12506,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="434">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -12526,7 +12534,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="435">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -12554,7 +12562,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="436">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -12582,7 +12590,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="437">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -12610,7 +12618,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="438">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -12638,7 +12646,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="439">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -12666,7 +12674,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="440">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -12694,7 +12702,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="441">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -12722,7 +12730,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="442">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -12750,7 +12758,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="443">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -12778,7 +12786,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="444">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -12806,7 +12814,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="445">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -12834,7 +12842,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="446">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -12862,7 +12870,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="447">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -12890,7 +12898,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="448">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -12918,7 +12926,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="449">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -12946,7 +12954,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="450">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -12974,7 +12982,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="451">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -13002,7 +13010,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="452">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -13030,7 +13038,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="453">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -13058,7 +13066,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="454">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -13086,7 +13094,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="455">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -13114,7 +13122,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="456">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -13142,7 +13150,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="457">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -13170,7 +13178,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="458">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -13198,7 +13206,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="459">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -13226,7 +13234,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="460">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -13254,7 +13262,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="461">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -13282,7 +13290,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="462">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -13310,7 +13318,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="463">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -13338,7 +13346,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="464">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -13366,7 +13374,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="465">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -13394,7 +13402,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="466">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -13422,7 +13430,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="467">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -13450,7 +13458,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="468">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -13478,7 +13486,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="469">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -13506,7 +13514,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="470">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -13534,7 +13542,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="471">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -13562,7 +13570,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="472">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -13590,7 +13598,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="473">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -13618,7 +13626,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="474">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -13646,7 +13654,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="475">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -13674,7 +13682,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="476">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -13702,7 +13710,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="477">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -13730,7 +13738,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="478">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -13758,7 +13766,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="479">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -13786,7 +13794,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="480">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -13814,7 +13822,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="481">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -13842,7 +13850,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="482">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -13870,7 +13878,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="483">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -13898,7 +13906,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="484">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -13926,7 +13934,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="485">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -13954,7 +13962,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="486">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -13982,7 +13990,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="487">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -14010,7 +14018,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="488">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -14038,7 +14046,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="489">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -14066,7 +14074,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="490">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -14094,7 +14102,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="491">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -14122,7 +14130,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="492">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -14150,7 +14158,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="493">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -14178,7 +14186,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="494">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -14206,7 +14214,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="495">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -14234,7 +14242,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="496">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -14262,7 +14270,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="497">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -14290,7 +14298,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="498">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -14318,7 +14326,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="499">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -14346,7 +14354,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="500">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -14374,7 +14382,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="501">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -14402,7 +14410,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="502">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -14430,7 +14438,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="503">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -14458,7 +14466,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="504">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -14486,7 +14494,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="505">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -14514,7 +14522,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="506">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -14542,7 +14550,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="507">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -14570,7 +14578,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="508">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -14598,7 +14606,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="509">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -14626,7 +14634,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="510">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -14654,7 +14662,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="511">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -14682,7 +14690,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="512">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -14710,7 +14718,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="513">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -14738,7 +14746,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="514">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -14766,7 +14774,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="515">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -14794,7 +14802,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="516">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -14822,7 +14830,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="517">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -14850,7 +14858,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="518">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -14878,7 +14886,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="519">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -14906,7 +14914,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="520">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -14934,7 +14942,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="521">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -14962,7 +14970,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="522">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -14990,7 +14998,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="523">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -15018,7 +15026,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="524">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -15046,7 +15054,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="525">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -15074,7 +15082,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="526">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -15102,7 +15110,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="527">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -15130,7 +15138,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="528">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -15158,7 +15166,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="529">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -15186,7 +15194,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="530">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -15214,7 +15222,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="531">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -15242,7 +15250,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="532">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -15270,7 +15278,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="533">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -15298,7 +15306,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="534">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -15326,7 +15334,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="535">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -15354,7 +15362,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="536">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -15382,7 +15390,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="537">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -15410,7 +15418,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="538">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -15438,7 +15446,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="539">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -15466,7 +15474,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="540">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -15494,7 +15502,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="541">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -15522,7 +15530,7 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="542">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -15550,7 +15558,7 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="543">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -15578,7 +15586,7 @@
       <c r="Y543" s="1"/>
       <c r="Z543" s="1"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="544">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -15606,7 +15614,7 @@
       <c r="Y544" s="1"/>
       <c r="Z544" s="1"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="545">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -15634,7 +15642,7 @@
       <c r="Y545" s="1"/>
       <c r="Z545" s="1"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="546">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -15662,7 +15670,7 @@
       <c r="Y546" s="1"/>
       <c r="Z546" s="1"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="547">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -15690,7 +15698,7 @@
       <c r="Y547" s="1"/>
       <c r="Z547" s="1"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="548">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -15718,7 +15726,7 @@
       <c r="Y548" s="1"/>
       <c r="Z548" s="1"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="549">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -15746,7 +15754,7 @@
       <c r="Y549" s="1"/>
       <c r="Z549" s="1"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="550">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -15774,7 +15782,7 @@
       <c r="Y550" s="1"/>
       <c r="Z550" s="1"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="551">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -15802,7 +15810,7 @@
       <c r="Y551" s="1"/>
       <c r="Z551" s="1"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="552">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -15830,7 +15838,7 @@
       <c r="Y552" s="1"/>
       <c r="Z552" s="1"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="553">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -15858,7 +15866,7 @@
       <c r="Y553" s="1"/>
       <c r="Z553" s="1"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="554">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -15886,7 +15894,7 @@
       <c r="Y554" s="1"/>
       <c r="Z554" s="1"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="555">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -15914,7 +15922,7 @@
       <c r="Y555" s="1"/>
       <c r="Z555" s="1"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="556">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -15942,7 +15950,7 @@
       <c r="Y556" s="1"/>
       <c r="Z556" s="1"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="557">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -15970,7 +15978,7 @@
       <c r="Y557" s="1"/>
       <c r="Z557" s="1"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="558">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -15998,7 +16006,7 @@
       <c r="Y558" s="1"/>
       <c r="Z558" s="1"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="559">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -16026,7 +16034,7 @@
       <c r="Y559" s="1"/>
       <c r="Z559" s="1"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="560">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -16054,7 +16062,7 @@
       <c r="Y560" s="1"/>
       <c r="Z560" s="1"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="561">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -16082,7 +16090,7 @@
       <c r="Y561" s="1"/>
       <c r="Z561" s="1"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="562">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -16110,7 +16118,7 @@
       <c r="Y562" s="1"/>
       <c r="Z562" s="1"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="563">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -16138,7 +16146,7 @@
       <c r="Y563" s="1"/>
       <c r="Z563" s="1"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="564">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -16166,7 +16174,7 @@
       <c r="Y564" s="1"/>
       <c r="Z564" s="1"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="565">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -16194,7 +16202,7 @@
       <c r="Y565" s="1"/>
       <c r="Z565" s="1"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="566">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -16222,7 +16230,7 @@
       <c r="Y566" s="1"/>
       <c r="Z566" s="1"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="567">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -16250,7 +16258,7 @@
       <c r="Y567" s="1"/>
       <c r="Z567" s="1"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="568">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -16278,7 +16286,7 @@
       <c r="Y568" s="1"/>
       <c r="Z568" s="1"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="569">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -16306,7 +16314,7 @@
       <c r="Y569" s="1"/>
       <c r="Z569" s="1"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="570">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -16334,7 +16342,7 @@
       <c r="Y570" s="1"/>
       <c r="Z570" s="1"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="571">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -16362,7 +16370,7 @@
       <c r="Y571" s="1"/>
       <c r="Z571" s="1"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="572">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -16390,7 +16398,7 @@
       <c r="Y572" s="1"/>
       <c r="Z572" s="1"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="573">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -16418,7 +16426,7 @@
       <c r="Y573" s="1"/>
       <c r="Z573" s="1"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="574">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -16446,7 +16454,7 @@
       <c r="Y574" s="1"/>
       <c r="Z574" s="1"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="575">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -16474,7 +16482,7 @@
       <c r="Y575" s="1"/>
       <c r="Z575" s="1"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="576">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -16502,7 +16510,7 @@
       <c r="Y576" s="1"/>
       <c r="Z576" s="1"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="577">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -16530,7 +16538,7 @@
       <c r="Y577" s="1"/>
       <c r="Z577" s="1"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="578">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -16558,7 +16566,7 @@
       <c r="Y578" s="1"/>
       <c r="Z578" s="1"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="579">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -16586,7 +16594,7 @@
       <c r="Y579" s="1"/>
       <c r="Z579" s="1"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="580">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -16614,7 +16622,7 @@
       <c r="Y580" s="1"/>
       <c r="Z580" s="1"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="581">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -16642,7 +16650,7 @@
       <c r="Y581" s="1"/>
       <c r="Z581" s="1"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="582">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -16670,7 +16678,7 @@
       <c r="Y582" s="1"/>
       <c r="Z582" s="1"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="583">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -16698,7 +16706,7 @@
       <c r="Y583" s="1"/>
       <c r="Z583" s="1"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="584">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -16726,7 +16734,7 @@
       <c r="Y584" s="1"/>
       <c r="Z584" s="1"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="585">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -16754,7 +16762,7 @@
       <c r="Y585" s="1"/>
       <c r="Z585" s="1"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="586">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -16782,7 +16790,7 @@
       <c r="Y586" s="1"/>
       <c r="Z586" s="1"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="587">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -16810,7 +16818,7 @@
       <c r="Y587" s="1"/>
       <c r="Z587" s="1"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="588">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -16838,7 +16846,7 @@
       <c r="Y588" s="1"/>
       <c r="Z588" s="1"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="589">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -16866,7 +16874,7 @@
       <c r="Y589" s="1"/>
       <c r="Z589" s="1"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="590">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -16894,7 +16902,7 @@
       <c r="Y590" s="1"/>
       <c r="Z590" s="1"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="591">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -16922,7 +16930,7 @@
       <c r="Y591" s="1"/>
       <c r="Z591" s="1"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="592">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -16950,7 +16958,7 @@
       <c r="Y592" s="1"/>
       <c r="Z592" s="1"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="593">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -16978,7 +16986,7 @@
       <c r="Y593" s="1"/>
       <c r="Z593" s="1"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="594">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -17006,7 +17014,7 @@
       <c r="Y594" s="1"/>
       <c r="Z594" s="1"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="595">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -17034,7 +17042,7 @@
       <c r="Y595" s="1"/>
       <c r="Z595" s="1"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="596">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -17062,7 +17070,7 @@
       <c r="Y596" s="1"/>
       <c r="Z596" s="1"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="597">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -17090,7 +17098,7 @@
       <c r="Y597" s="1"/>
       <c r="Z597" s="1"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="598">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -17118,7 +17126,7 @@
       <c r="Y598" s="1"/>
       <c r="Z598" s="1"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="599">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -17146,7 +17154,7 @@
       <c r="Y599" s="1"/>
       <c r="Z599" s="1"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="600">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -17174,7 +17182,7 @@
       <c r="Y600" s="1"/>
       <c r="Z600" s="1"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="601">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -17202,7 +17210,7 @@
       <c r="Y601" s="1"/>
       <c r="Z601" s="1"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="602">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -17230,7 +17238,7 @@
       <c r="Y602" s="1"/>
       <c r="Z602" s="1"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="603">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -17258,7 +17266,7 @@
       <c r="Y603" s="1"/>
       <c r="Z603" s="1"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="604">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -17286,7 +17294,7 @@
       <c r="Y604" s="1"/>
       <c r="Z604" s="1"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="605">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -17314,7 +17322,7 @@
       <c r="Y605" s="1"/>
       <c r="Z605" s="1"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="606">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -17342,7 +17350,7 @@
       <c r="Y606" s="1"/>
       <c r="Z606" s="1"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="607">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -17370,7 +17378,7 @@
       <c r="Y607" s="1"/>
       <c r="Z607" s="1"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="608">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -17398,7 +17406,7 @@
       <c r="Y608" s="1"/>
       <c r="Z608" s="1"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="609">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -17426,7 +17434,7 @@
       <c r="Y609" s="1"/>
       <c r="Z609" s="1"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="610">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -17454,7 +17462,7 @@
       <c r="Y610" s="1"/>
       <c r="Z610" s="1"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="611">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -17482,7 +17490,7 @@
       <c r="Y611" s="1"/>
       <c r="Z611" s="1"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="612">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -17510,7 +17518,7 @@
       <c r="Y612" s="1"/>
       <c r="Z612" s="1"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="613">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -17538,7 +17546,7 @@
       <c r="Y613" s="1"/>
       <c r="Z613" s="1"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="614">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -17566,7 +17574,7 @@
       <c r="Y614" s="1"/>
       <c r="Z614" s="1"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="615">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -17594,7 +17602,7 @@
       <c r="Y615" s="1"/>
       <c r="Z615" s="1"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="616">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -17622,7 +17630,7 @@
       <c r="Y616" s="1"/>
       <c r="Z616" s="1"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="617">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -17650,7 +17658,7 @@
       <c r="Y617" s="1"/>
       <c r="Z617" s="1"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="618">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -17678,7 +17686,7 @@
       <c r="Y618" s="1"/>
       <c r="Z618" s="1"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="619">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -17706,7 +17714,7 @@
       <c r="Y619" s="1"/>
       <c r="Z619" s="1"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="620">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -17734,7 +17742,7 @@
       <c r="Y620" s="1"/>
       <c r="Z620" s="1"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="621">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -17762,7 +17770,7 @@
       <c r="Y621" s="1"/>
       <c r="Z621" s="1"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="622">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -17790,7 +17798,7 @@
       <c r="Y622" s="1"/>
       <c r="Z622" s="1"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="623">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -17818,7 +17826,7 @@
       <c r="Y623" s="1"/>
       <c r="Z623" s="1"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="624">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -17846,7 +17854,7 @@
       <c r="Y624" s="1"/>
       <c r="Z624" s="1"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="625">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -17874,7 +17882,7 @@
       <c r="Y625" s="1"/>
       <c r="Z625" s="1"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="626">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -17902,7 +17910,7 @@
       <c r="Y626" s="1"/>
       <c r="Z626" s="1"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="627">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -17930,7 +17938,7 @@
       <c r="Y627" s="1"/>
       <c r="Z627" s="1"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="628">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -17958,7 +17966,7 @@
       <c r="Y628" s="1"/>
       <c r="Z628" s="1"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="629">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -17986,7 +17994,7 @@
       <c r="Y629" s="1"/>
       <c r="Z629" s="1"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="630">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -18014,7 +18022,7 @@
       <c r="Y630" s="1"/>
       <c r="Z630" s="1"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="631">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -18042,7 +18050,7 @@
       <c r="Y631" s="1"/>
       <c r="Z631" s="1"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="632">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -18070,7 +18078,7 @@
       <c r="Y632" s="1"/>
       <c r="Z632" s="1"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="633">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -18098,7 +18106,7 @@
       <c r="Y633" s="1"/>
       <c r="Z633" s="1"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="634">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -18126,7 +18134,7 @@
       <c r="Y634" s="1"/>
       <c r="Z634" s="1"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="635">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -18154,7 +18162,7 @@
       <c r="Y635" s="1"/>
       <c r="Z635" s="1"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="636">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -18182,7 +18190,7 @@
       <c r="Y636" s="1"/>
       <c r="Z636" s="1"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="637">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -18210,7 +18218,7 @@
       <c r="Y637" s="1"/>
       <c r="Z637" s="1"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="638">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -18238,7 +18246,7 @@
       <c r="Y638" s="1"/>
       <c r="Z638" s="1"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="639">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -18266,7 +18274,7 @@
       <c r="Y639" s="1"/>
       <c r="Z639" s="1"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="640">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -18294,7 +18302,7 @@
       <c r="Y640" s="1"/>
       <c r="Z640" s="1"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="641">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -18322,7 +18330,7 @@
       <c r="Y641" s="1"/>
       <c r="Z641" s="1"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="642">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -18350,7 +18358,7 @@
       <c r="Y642" s="1"/>
       <c r="Z642" s="1"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="643">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -18378,7 +18386,7 @@
       <c r="Y643" s="1"/>
       <c r="Z643" s="1"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="644">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -18406,7 +18414,7 @@
       <c r="Y644" s="1"/>
       <c r="Z644" s="1"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="645">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -18434,7 +18442,7 @@
       <c r="Y645" s="1"/>
       <c r="Z645" s="1"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="646">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -18462,7 +18470,7 @@
       <c r="Y646" s="1"/>
       <c r="Z646" s="1"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="647">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -18490,7 +18498,7 @@
       <c r="Y647" s="1"/>
       <c r="Z647" s="1"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="648">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -18518,7 +18526,7 @@
       <c r="Y648" s="1"/>
       <c r="Z648" s="1"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="649">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -18546,7 +18554,7 @@
       <c r="Y649" s="1"/>
       <c r="Z649" s="1"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="650">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -18574,7 +18582,7 @@
       <c r="Y650" s="1"/>
       <c r="Z650" s="1"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="651">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -18602,7 +18610,7 @@
       <c r="Y651" s="1"/>
       <c r="Z651" s="1"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="652">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -18630,7 +18638,7 @@
       <c r="Y652" s="1"/>
       <c r="Z652" s="1"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="653">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -18658,7 +18666,7 @@
       <c r="Y653" s="1"/>
       <c r="Z653" s="1"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="654">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -18686,7 +18694,7 @@
       <c r="Y654" s="1"/>
       <c r="Z654" s="1"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="655">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -18714,7 +18722,7 @@
       <c r="Y655" s="1"/>
       <c r="Z655" s="1"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="656">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -18742,7 +18750,7 @@
       <c r="Y656" s="1"/>
       <c r="Z656" s="1"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="657">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -18770,7 +18778,7 @@
       <c r="Y657" s="1"/>
       <c r="Z657" s="1"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="658">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -18798,7 +18806,7 @@
       <c r="Y658" s="1"/>
       <c r="Z658" s="1"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="659">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -18826,7 +18834,7 @@
       <c r="Y659" s="1"/>
       <c r="Z659" s="1"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="660">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -18854,7 +18862,7 @@
       <c r="Y660" s="1"/>
       <c r="Z660" s="1"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="661">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -18882,7 +18890,7 @@
       <c r="Y661" s="1"/>
       <c r="Z661" s="1"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="662">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -18910,7 +18918,7 @@
       <c r="Y662" s="1"/>
       <c r="Z662" s="1"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="663">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -18938,7 +18946,7 @@
       <c r="Y663" s="1"/>
       <c r="Z663" s="1"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="664">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -18966,7 +18974,7 @@
       <c r="Y664" s="1"/>
       <c r="Z664" s="1"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="665">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -18994,7 +19002,7 @@
       <c r="Y665" s="1"/>
       <c r="Z665" s="1"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="666">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -19022,7 +19030,7 @@
       <c r="Y666" s="1"/>
       <c r="Z666" s="1"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="667">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -19050,7 +19058,7 @@
       <c r="Y667" s="1"/>
       <c r="Z667" s="1"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="668">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -19078,7 +19086,7 @@
       <c r="Y668" s="1"/>
       <c r="Z668" s="1"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="669">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -19106,7 +19114,7 @@
       <c r="Y669" s="1"/>
       <c r="Z669" s="1"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="670">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -19134,7 +19142,7 @@
       <c r="Y670" s="1"/>
       <c r="Z670" s="1"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="671">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -19162,7 +19170,7 @@
       <c r="Y671" s="1"/>
       <c r="Z671" s="1"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="672">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -19190,7 +19198,7 @@
       <c r="Y672" s="1"/>
       <c r="Z672" s="1"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="673">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -19218,7 +19226,7 @@
       <c r="Y673" s="1"/>
       <c r="Z673" s="1"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="674">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -19246,7 +19254,7 @@
       <c r="Y674" s="1"/>
       <c r="Z674" s="1"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="675">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -19274,7 +19282,7 @@
       <c r="Y675" s="1"/>
       <c r="Z675" s="1"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="676">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -19302,7 +19310,7 @@
       <c r="Y676" s="1"/>
       <c r="Z676" s="1"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="677">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -19330,7 +19338,7 @@
       <c r="Y677" s="1"/>
       <c r="Z677" s="1"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="678">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -19358,7 +19366,7 @@
       <c r="Y678" s="1"/>
       <c r="Z678" s="1"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="679">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -19386,7 +19394,7 @@
       <c r="Y679" s="1"/>
       <c r="Z679" s="1"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="680">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -19414,7 +19422,7 @@
       <c r="Y680" s="1"/>
       <c r="Z680" s="1"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="681">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -19442,7 +19450,7 @@
       <c r="Y681" s="1"/>
       <c r="Z681" s="1"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="682">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -19470,7 +19478,7 @@
       <c r="Y682" s="1"/>
       <c r="Z682" s="1"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="683">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -19498,7 +19506,7 @@
       <c r="Y683" s="1"/>
       <c r="Z683" s="1"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="684">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -19526,7 +19534,7 @@
       <c r="Y684" s="1"/>
       <c r="Z684" s="1"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="685">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -19554,7 +19562,7 @@
       <c r="Y685" s="1"/>
       <c r="Z685" s="1"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="686">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -19582,7 +19590,7 @@
       <c r="Y686" s="1"/>
       <c r="Z686" s="1"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="687">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -19610,7 +19618,7 @@
       <c r="Y687" s="1"/>
       <c r="Z687" s="1"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="688">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -19638,7 +19646,7 @@
       <c r="Y688" s="1"/>
       <c r="Z688" s="1"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="689">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -19666,7 +19674,7 @@
       <c r="Y689" s="1"/>
       <c r="Z689" s="1"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="690">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -19694,7 +19702,7 @@
       <c r="Y690" s="1"/>
       <c r="Z690" s="1"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="691">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -19722,7 +19730,7 @@
       <c r="Y691" s="1"/>
       <c r="Z691" s="1"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="692">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -19750,7 +19758,7 @@
       <c r="Y692" s="1"/>
       <c r="Z692" s="1"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="693">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -19778,7 +19786,7 @@
       <c r="Y693" s="1"/>
       <c r="Z693" s="1"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="694">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -19806,7 +19814,7 @@
       <c r="Y694" s="1"/>
       <c r="Z694" s="1"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="695">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -19834,7 +19842,7 @@
       <c r="Y695" s="1"/>
       <c r="Z695" s="1"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="696">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -19862,7 +19870,7 @@
       <c r="Y696" s="1"/>
       <c r="Z696" s="1"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="697">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -19890,7 +19898,7 @@
       <c r="Y697" s="1"/>
       <c r="Z697" s="1"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="698">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -19918,7 +19926,7 @@
       <c r="Y698" s="1"/>
       <c r="Z698" s="1"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="699">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -19946,7 +19954,7 @@
       <c r="Y699" s="1"/>
       <c r="Z699" s="1"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="700">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -19974,7 +19982,7 @@
       <c r="Y700" s="1"/>
       <c r="Z700" s="1"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="701">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -20002,7 +20010,7 @@
       <c r="Y701" s="1"/>
       <c r="Z701" s="1"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="702">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -20030,7 +20038,7 @@
       <c r="Y702" s="1"/>
       <c r="Z702" s="1"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="703">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -20058,7 +20066,7 @@
       <c r="Y703" s="1"/>
       <c r="Z703" s="1"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="704">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -20086,7 +20094,7 @@
       <c r="Y704" s="1"/>
       <c r="Z704" s="1"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="705">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -20114,7 +20122,7 @@
       <c r="Y705" s="1"/>
       <c r="Z705" s="1"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="706">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -20142,7 +20150,7 @@
       <c r="Y706" s="1"/>
       <c r="Z706" s="1"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="707">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -20170,7 +20178,7 @@
       <c r="Y707" s="1"/>
       <c r="Z707" s="1"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="708">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -20198,7 +20206,7 @@
       <c r="Y708" s="1"/>
       <c r="Z708" s="1"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="709">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -20226,7 +20234,7 @@
       <c r="Y709" s="1"/>
       <c r="Z709" s="1"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="710">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -20254,7 +20262,7 @@
       <c r="Y710" s="1"/>
       <c r="Z710" s="1"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="711">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -20282,7 +20290,7 @@
       <c r="Y711" s="1"/>
       <c r="Z711" s="1"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="712">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -20310,7 +20318,7 @@
       <c r="Y712" s="1"/>
       <c r="Z712" s="1"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="713">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -20338,7 +20346,7 @@
       <c r="Y713" s="1"/>
       <c r="Z713" s="1"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="714">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -20366,7 +20374,7 @@
       <c r="Y714" s="1"/>
       <c r="Z714" s="1"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="715">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -20394,7 +20402,7 @@
       <c r="Y715" s="1"/>
       <c r="Z715" s="1"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="716">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -20422,7 +20430,7 @@
       <c r="Y716" s="1"/>
       <c r="Z716" s="1"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="717">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -20450,7 +20458,7 @@
       <c r="Y717" s="1"/>
       <c r="Z717" s="1"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="718">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -20478,7 +20486,7 @@
       <c r="Y718" s="1"/>
       <c r="Z718" s="1"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="719">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -20506,7 +20514,7 @@
       <c r="Y719" s="1"/>
       <c r="Z719" s="1"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="720">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -20534,7 +20542,7 @@
       <c r="Y720" s="1"/>
       <c r="Z720" s="1"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="721">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -20562,7 +20570,7 @@
       <c r="Y721" s="1"/>
       <c r="Z721" s="1"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="722">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -20590,7 +20598,7 @@
       <c r="Y722" s="1"/>
       <c r="Z722" s="1"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="723">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -20618,7 +20626,7 @@
       <c r="Y723" s="1"/>
       <c r="Z723" s="1"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="724">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -20646,7 +20654,7 @@
       <c r="Y724" s="1"/>
       <c r="Z724" s="1"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="725">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -20674,7 +20682,7 @@
       <c r="Y725" s="1"/>
       <c r="Z725" s="1"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="726">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -20702,7 +20710,7 @@
       <c r="Y726" s="1"/>
       <c r="Z726" s="1"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="727">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -20730,7 +20738,7 @@
       <c r="Y727" s="1"/>
       <c r="Z727" s="1"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="728">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -20758,7 +20766,7 @@
       <c r="Y728" s="1"/>
       <c r="Z728" s="1"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="729">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -20786,7 +20794,7 @@
       <c r="Y729" s="1"/>
       <c r="Z729" s="1"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="730">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -20814,7 +20822,7 @@
       <c r="Y730" s="1"/>
       <c r="Z730" s="1"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="731">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -20842,7 +20850,7 @@
       <c r="Y731" s="1"/>
       <c r="Z731" s="1"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="732">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -20870,7 +20878,7 @@
       <c r="Y732" s="1"/>
       <c r="Z732" s="1"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="733">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -20898,7 +20906,7 @@
       <c r="Y733" s="1"/>
       <c r="Z733" s="1"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="734">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -20926,7 +20934,7 @@
       <c r="Y734" s="1"/>
       <c r="Z734" s="1"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="735">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -20954,7 +20962,7 @@
       <c r="Y735" s="1"/>
       <c r="Z735" s="1"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="736">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -20982,7 +20990,7 @@
       <c r="Y736" s="1"/>
       <c r="Z736" s="1"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="737">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -21010,7 +21018,7 @@
       <c r="Y737" s="1"/>
       <c r="Z737" s="1"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="738">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -21038,7 +21046,7 @@
       <c r="Y738" s="1"/>
       <c r="Z738" s="1"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="739">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -21066,7 +21074,7 @@
       <c r="Y739" s="1"/>
       <c r="Z739" s="1"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="740">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -21094,7 +21102,7 @@
       <c r="Y740" s="1"/>
       <c r="Z740" s="1"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="741">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -21122,7 +21130,7 @@
       <c r="Y741" s="1"/>
       <c r="Z741" s="1"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="742">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -21150,7 +21158,7 @@
       <c r="Y742" s="1"/>
       <c r="Z742" s="1"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="743">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -21178,7 +21186,7 @@
       <c r="Y743" s="1"/>
       <c r="Z743" s="1"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="744">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -21206,7 +21214,7 @@
       <c r="Y744" s="1"/>
       <c r="Z744" s="1"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="745">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -21234,7 +21242,7 @@
       <c r="Y745" s="1"/>
       <c r="Z745" s="1"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="746">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -21262,7 +21270,7 @@
       <c r="Y746" s="1"/>
       <c r="Z746" s="1"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="747">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -21290,7 +21298,7 @@
       <c r="Y747" s="1"/>
       <c r="Z747" s="1"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="748">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -21318,7 +21326,7 @@
       <c r="Y748" s="1"/>
       <c r="Z748" s="1"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="749">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -21346,7 +21354,7 @@
       <c r="Y749" s="1"/>
       <c r="Z749" s="1"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="750">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -21374,7 +21382,7 @@
       <c r="Y750" s="1"/>
       <c r="Z750" s="1"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="751">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -21402,7 +21410,7 @@
       <c r="Y751" s="1"/>
       <c r="Z751" s="1"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="752">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -21430,7 +21438,7 @@
       <c r="Y752" s="1"/>
       <c r="Z752" s="1"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="753">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -21458,7 +21466,7 @@
       <c r="Y753" s="1"/>
       <c r="Z753" s="1"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="754">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -21486,7 +21494,7 @@
       <c r="Y754" s="1"/>
       <c r="Z754" s="1"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="755">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -21514,7 +21522,7 @@
       <c r="Y755" s="1"/>
       <c r="Z755" s="1"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="756">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -21542,7 +21550,7 @@
       <c r="Y756" s="1"/>
       <c r="Z756" s="1"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="757">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -21570,7 +21578,7 @@
       <c r="Y757" s="1"/>
       <c r="Z757" s="1"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="758">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -21598,7 +21606,7 @@
       <c r="Y758" s="1"/>
       <c r="Z758" s="1"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="759">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -21626,7 +21634,7 @@
       <c r="Y759" s="1"/>
       <c r="Z759" s="1"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="760">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -21654,7 +21662,7 @@
       <c r="Y760" s="1"/>
       <c r="Z760" s="1"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="761">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -21682,7 +21690,7 @@
       <c r="Y761" s="1"/>
       <c r="Z761" s="1"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="762">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -21710,7 +21718,7 @@
       <c r="Y762" s="1"/>
       <c r="Z762" s="1"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="763">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -21738,7 +21746,7 @@
       <c r="Y763" s="1"/>
       <c r="Z763" s="1"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="764">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -21766,7 +21774,7 @@
       <c r="Y764" s="1"/>
       <c r="Z764" s="1"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="765">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -21794,7 +21802,7 @@
       <c r="Y765" s="1"/>
       <c r="Z765" s="1"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="766">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -21822,7 +21830,7 @@
       <c r="Y766" s="1"/>
       <c r="Z766" s="1"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="767">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -21850,7 +21858,7 @@
       <c r="Y767" s="1"/>
       <c r="Z767" s="1"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="768">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -21878,7 +21886,7 @@
       <c r="Y768" s="1"/>
       <c r="Z768" s="1"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="769">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -21906,7 +21914,7 @@
       <c r="Y769" s="1"/>
       <c r="Z769" s="1"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="770">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -21934,7 +21942,7 @@
       <c r="Y770" s="1"/>
       <c r="Z770" s="1"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="771">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -21962,7 +21970,7 @@
       <c r="Y771" s="1"/>
       <c r="Z771" s="1"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="772">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -21990,7 +21998,7 @@
       <c r="Y772" s="1"/>
       <c r="Z772" s="1"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="773">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -22018,7 +22026,7 @@
       <c r="Y773" s="1"/>
       <c r="Z773" s="1"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="774">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -22046,7 +22054,7 @@
       <c r="Y774" s="1"/>
       <c r="Z774" s="1"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="775">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -22074,7 +22082,7 @@
       <c r="Y775" s="1"/>
       <c r="Z775" s="1"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="776">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -22102,7 +22110,7 @@
       <c r="Y776" s="1"/>
       <c r="Z776" s="1"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="777">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -22130,7 +22138,7 @@
       <c r="Y777" s="1"/>
       <c r="Z777" s="1"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="778">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -22158,7 +22166,7 @@
       <c r="Y778" s="1"/>
       <c r="Z778" s="1"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="779">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -22186,7 +22194,7 @@
       <c r="Y779" s="1"/>
       <c r="Z779" s="1"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="780">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -22214,7 +22222,7 @@
       <c r="Y780" s="1"/>
       <c r="Z780" s="1"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="781">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -22242,7 +22250,7 @@
       <c r="Y781" s="1"/>
       <c r="Z781" s="1"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="782">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -22270,7 +22278,7 @@
       <c r="Y782" s="1"/>
       <c r="Z782" s="1"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="783">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -22298,7 +22306,7 @@
       <c r="Y783" s="1"/>
       <c r="Z783" s="1"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="784">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -22326,7 +22334,7 @@
       <c r="Y784" s="1"/>
       <c r="Z784" s="1"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="785">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -22354,7 +22362,7 @@
       <c r="Y785" s="1"/>
       <c r="Z785" s="1"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="786">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -22382,7 +22390,7 @@
       <c r="Y786" s="1"/>
       <c r="Z786" s="1"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="787">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -22410,7 +22418,7 @@
       <c r="Y787" s="1"/>
       <c r="Z787" s="1"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="788">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -22438,7 +22446,7 @@
       <c r="Y788" s="1"/>
       <c r="Z788" s="1"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="789">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -22466,7 +22474,7 @@
       <c r="Y789" s="1"/>
       <c r="Z789" s="1"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="790">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -22494,7 +22502,7 @@
       <c r="Y790" s="1"/>
       <c r="Z790" s="1"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="791">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -22522,7 +22530,7 @@
       <c r="Y791" s="1"/>
       <c r="Z791" s="1"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="792">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -22550,7 +22558,7 @@
       <c r="Y792" s="1"/>
       <c r="Z792" s="1"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="793">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -22578,7 +22586,7 @@
       <c r="Y793" s="1"/>
       <c r="Z793" s="1"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="794">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -22606,7 +22614,7 @@
       <c r="Y794" s="1"/>
       <c r="Z794" s="1"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="795">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -22634,7 +22642,7 @@
       <c r="Y795" s="1"/>
       <c r="Z795" s="1"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="796">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -22662,7 +22670,7 @@
       <c r="Y796" s="1"/>
       <c r="Z796" s="1"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="797">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -22690,7 +22698,7 @@
       <c r="Y797" s="1"/>
       <c r="Z797" s="1"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="798">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -22718,7 +22726,7 @@
       <c r="Y798" s="1"/>
       <c r="Z798" s="1"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="799">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -22746,7 +22754,7 @@
       <c r="Y799" s="1"/>
       <c r="Z799" s="1"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="800">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -22774,7 +22782,7 @@
       <c r="Y800" s="1"/>
       <c r="Z800" s="1"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="801">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -22802,7 +22810,7 @@
       <c r="Y801" s="1"/>
       <c r="Z801" s="1"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="802">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -22830,7 +22838,7 @@
       <c r="Y802" s="1"/>
       <c r="Z802" s="1"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="803">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -22858,7 +22866,7 @@
       <c r="Y803" s="1"/>
       <c r="Z803" s="1"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="804">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -22886,7 +22894,7 @@
       <c r="Y804" s="1"/>
       <c r="Z804" s="1"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="805">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -22914,7 +22922,7 @@
       <c r="Y805" s="1"/>
       <c r="Z805" s="1"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="806">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -22942,7 +22950,7 @@
       <c r="Y806" s="1"/>
       <c r="Z806" s="1"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="807">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -22970,7 +22978,7 @@
       <c r="Y807" s="1"/>
       <c r="Z807" s="1"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="808">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -22998,7 +23006,7 @@
       <c r="Y808" s="1"/>
       <c r="Z808" s="1"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="809">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -23026,7 +23034,7 @@
       <c r="Y809" s="1"/>
       <c r="Z809" s="1"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="810">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -23054,7 +23062,7 @@
       <c r="Y810" s="1"/>
       <c r="Z810" s="1"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="811">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -23082,7 +23090,7 @@
       <c r="Y811" s="1"/>
       <c r="Z811" s="1"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="812">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -23110,7 +23118,7 @@
       <c r="Y812" s="1"/>
       <c r="Z812" s="1"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="813">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -23138,7 +23146,7 @@
       <c r="Y813" s="1"/>
       <c r="Z813" s="1"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="814">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -23166,7 +23174,7 @@
       <c r="Y814" s="1"/>
       <c r="Z814" s="1"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="815">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -23194,7 +23202,7 @@
       <c r="Y815" s="1"/>
       <c r="Z815" s="1"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="816">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -23222,7 +23230,7 @@
       <c r="Y816" s="1"/>
       <c r="Z816" s="1"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="817">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -23250,7 +23258,7 @@
       <c r="Y817" s="1"/>
       <c r="Z817" s="1"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="818">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -23278,7 +23286,7 @@
       <c r="Y818" s="1"/>
       <c r="Z818" s="1"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="819">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -23306,7 +23314,7 @@
       <c r="Y819" s="1"/>
       <c r="Z819" s="1"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="820">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -23334,7 +23342,7 @@
       <c r="Y820" s="1"/>
       <c r="Z820" s="1"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="821">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -23362,7 +23370,7 @@
       <c r="Y821" s="1"/>
       <c r="Z821" s="1"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="822">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -23390,7 +23398,7 @@
       <c r="Y822" s="1"/>
       <c r="Z822" s="1"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="823">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -23418,7 +23426,7 @@
       <c r="Y823" s="1"/>
       <c r="Z823" s="1"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="824">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -23446,7 +23454,7 @@
       <c r="Y824" s="1"/>
       <c r="Z824" s="1"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="825">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -23474,7 +23482,7 @@
       <c r="Y825" s="1"/>
       <c r="Z825" s="1"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="826">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -23502,7 +23510,7 @@
       <c r="Y826" s="1"/>
       <c r="Z826" s="1"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="827">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -23530,7 +23538,7 @@
       <c r="Y827" s="1"/>
       <c r="Z827" s="1"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="828">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -23558,7 +23566,7 @@
       <c r="Y828" s="1"/>
       <c r="Z828" s="1"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="829">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -23586,7 +23594,7 @@
       <c r="Y829" s="1"/>
       <c r="Z829" s="1"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="830">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -23614,7 +23622,7 @@
       <c r="Y830" s="1"/>
       <c r="Z830" s="1"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="831">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -23642,7 +23650,7 @@
       <c r="Y831" s="1"/>
       <c r="Z831" s="1"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="832">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -23670,7 +23678,7 @@
       <c r="Y832" s="1"/>
       <c r="Z832" s="1"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="833">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -23698,7 +23706,7 @@
       <c r="Y833" s="1"/>
       <c r="Z833" s="1"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="834">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -23726,7 +23734,7 @@
       <c r="Y834" s="1"/>
       <c r="Z834" s="1"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="835">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -23754,7 +23762,7 @@
       <c r="Y835" s="1"/>
       <c r="Z835" s="1"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="836">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -23782,7 +23790,7 @@
       <c r="Y836" s="1"/>
       <c r="Z836" s="1"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="837">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -23810,7 +23818,7 @@
       <c r="Y837" s="1"/>
       <c r="Z837" s="1"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="838">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -23838,7 +23846,7 @@
       <c r="Y838" s="1"/>
       <c r="Z838" s="1"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="839">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -23866,7 +23874,7 @@
       <c r="Y839" s="1"/>
       <c r="Z839" s="1"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="840">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -23894,7 +23902,7 @@
       <c r="Y840" s="1"/>
       <c r="Z840" s="1"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="841">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -23922,7 +23930,7 @@
       <c r="Y841" s="1"/>
       <c r="Z841" s="1"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="842">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -23950,7 +23958,7 @@
       <c r="Y842" s="1"/>
       <c r="Z842" s="1"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="843">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -23978,7 +23986,7 @@
       <c r="Y843" s="1"/>
       <c r="Z843" s="1"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="844">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -24006,7 +24014,7 @@
       <c r="Y844" s="1"/>
       <c r="Z844" s="1"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="845">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -24034,7 +24042,7 @@
       <c r="Y845" s="1"/>
       <c r="Z845" s="1"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="846">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -24062,7 +24070,7 @@
       <c r="Y846" s="1"/>
       <c r="Z846" s="1"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="847">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -24090,7 +24098,7 @@
       <c r="Y847" s="1"/>
       <c r="Z847" s="1"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="848">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -24118,7 +24126,7 @@
       <c r="Y848" s="1"/>
       <c r="Z848" s="1"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="849">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -24146,7 +24154,7 @@
       <c r="Y849" s="1"/>
       <c r="Z849" s="1"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="850">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -24174,7 +24182,7 @@
       <c r="Y850" s="1"/>
       <c r="Z850" s="1"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="851">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -24202,7 +24210,7 @@
       <c r="Y851" s="1"/>
       <c r="Z851" s="1"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="852">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -24230,7 +24238,7 @@
       <c r="Y852" s="1"/>
       <c r="Z852" s="1"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="853">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -24258,7 +24266,7 @@
       <c r="Y853" s="1"/>
       <c r="Z853" s="1"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="854">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -24286,7 +24294,7 @@
       <c r="Y854" s="1"/>
       <c r="Z854" s="1"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="855">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -24314,7 +24322,7 @@
       <c r="Y855" s="1"/>
       <c r="Z855" s="1"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="856">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -24342,7 +24350,7 @@
       <c r="Y856" s="1"/>
       <c r="Z856" s="1"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="857">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -24370,7 +24378,7 @@
       <c r="Y857" s="1"/>
       <c r="Z857" s="1"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="858">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -24398,7 +24406,7 @@
       <c r="Y858" s="1"/>
       <c r="Z858" s="1"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="859">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -24426,7 +24434,7 @@
       <c r="Y859" s="1"/>
       <c r="Z859" s="1"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="860">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -24454,7 +24462,7 @@
       <c r="Y860" s="1"/>
       <c r="Z860" s="1"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="861">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -24482,7 +24490,7 @@
       <c r="Y861" s="1"/>
       <c r="Z861" s="1"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="862">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -24510,7 +24518,7 @@
       <c r="Y862" s="1"/>
       <c r="Z862" s="1"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="863">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -24538,7 +24546,7 @@
       <c r="Y863" s="1"/>
       <c r="Z863" s="1"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="864">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -24566,7 +24574,7 @@
       <c r="Y864" s="1"/>
       <c r="Z864" s="1"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="865">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -24594,7 +24602,7 @@
       <c r="Y865" s="1"/>
       <c r="Z865" s="1"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="866">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -24622,7 +24630,7 @@
       <c r="Y866" s="1"/>
       <c r="Z866" s="1"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="867">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -24650,7 +24658,7 @@
       <c r="Y867" s="1"/>
       <c r="Z867" s="1"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="868">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -24678,7 +24686,7 @@
       <c r="Y868" s="1"/>
       <c r="Z868" s="1"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="869">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -24706,7 +24714,7 @@
       <c r="Y869" s="1"/>
       <c r="Z869" s="1"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="870">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -24734,7 +24742,7 @@
       <c r="Y870" s="1"/>
       <c r="Z870" s="1"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="871">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -24762,7 +24770,7 @@
       <c r="Y871" s="1"/>
       <c r="Z871" s="1"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="872">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -24790,7 +24798,7 @@
       <c r="Y872" s="1"/>
       <c r="Z872" s="1"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="873">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -24818,7 +24826,7 @@
       <c r="Y873" s="1"/>
       <c r="Z873" s="1"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="874">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -24846,7 +24854,7 @@
       <c r="Y874" s="1"/>
       <c r="Z874" s="1"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="875">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -24874,7 +24882,7 @@
       <c r="Y875" s="1"/>
       <c r="Z875" s="1"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="876">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -24902,7 +24910,7 @@
       <c r="Y876" s="1"/>
       <c r="Z876" s="1"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="877">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -24930,7 +24938,7 @@
       <c r="Y877" s="1"/>
       <c r="Z877" s="1"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="878">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -24958,7 +24966,7 @@
       <c r="Y878" s="1"/>
       <c r="Z878" s="1"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="879">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -24986,7 +24994,7 @@
       <c r="Y879" s="1"/>
       <c r="Z879" s="1"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="880">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -25014,7 +25022,7 @@
       <c r="Y880" s="1"/>
       <c r="Z880" s="1"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="881">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -25042,7 +25050,7 @@
       <c r="Y881" s="1"/>
       <c r="Z881" s="1"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="882">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -25070,7 +25078,7 @@
       <c r="Y882" s="1"/>
       <c r="Z882" s="1"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="883">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -25098,7 +25106,7 @@
       <c r="Y883" s="1"/>
       <c r="Z883" s="1"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="884">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -25126,7 +25134,7 @@
       <c r="Y884" s="1"/>
       <c r="Z884" s="1"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="885">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -25154,7 +25162,7 @@
       <c r="Y885" s="1"/>
       <c r="Z885" s="1"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="886">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -25182,7 +25190,7 @@
       <c r="Y886" s="1"/>
       <c r="Z886" s="1"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="887">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -25210,7 +25218,7 @@
       <c r="Y887" s="1"/>
       <c r="Z887" s="1"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="888">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -25238,7 +25246,7 @@
       <c r="Y888" s="1"/>
       <c r="Z888" s="1"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="889">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -25266,7 +25274,7 @@
       <c r="Y889" s="1"/>
       <c r="Z889" s="1"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="890">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -25294,7 +25302,7 @@
       <c r="Y890" s="1"/>
       <c r="Z890" s="1"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="891">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -25322,7 +25330,7 @@
       <c r="Y891" s="1"/>
       <c r="Z891" s="1"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="892">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -25350,7 +25358,7 @@
       <c r="Y892" s="1"/>
       <c r="Z892" s="1"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="893">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -25378,7 +25386,7 @@
       <c r="Y893" s="1"/>
       <c r="Z893" s="1"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="894">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -25406,7 +25414,7 @@
       <c r="Y894" s="1"/>
       <c r="Z894" s="1"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="895">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -25434,7 +25442,7 @@
       <c r="Y895" s="1"/>
       <c r="Z895" s="1"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="896">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -25462,7 +25470,7 @@
       <c r="Y896" s="1"/>
       <c r="Z896" s="1"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="897">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -25490,7 +25498,7 @@
       <c r="Y897" s="1"/>
       <c r="Z897" s="1"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="898">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -25518,7 +25526,7 @@
       <c r="Y898" s="1"/>
       <c r="Z898" s="1"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="899">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -25546,7 +25554,7 @@
       <c r="Y899" s="1"/>
       <c r="Z899" s="1"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="900">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -25574,7 +25582,7 @@
       <c r="Y900" s="1"/>
       <c r="Z900" s="1"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="901">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -25602,7 +25610,7 @@
       <c r="Y901" s="1"/>
       <c r="Z901" s="1"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="902">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -25630,7 +25638,7 @@
       <c r="Y902" s="1"/>
       <c r="Z902" s="1"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="903">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -25658,7 +25666,7 @@
       <c r="Y903" s="1"/>
       <c r="Z903" s="1"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="904">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -25686,7 +25694,7 @@
       <c r="Y904" s="1"/>
       <c r="Z904" s="1"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="905">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -25714,7 +25722,7 @@
       <c r="Y905" s="1"/>
       <c r="Z905" s="1"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="906">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -25742,7 +25750,7 @@
       <c r="Y906" s="1"/>
       <c r="Z906" s="1"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="907">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -25770,7 +25778,7 @@
       <c r="Y907" s="1"/>
       <c r="Z907" s="1"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="908">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -25798,7 +25806,7 @@
       <c r="Y908" s="1"/>
       <c r="Z908" s="1"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="909">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -25826,7 +25834,7 @@
       <c r="Y909" s="1"/>
       <c r="Z909" s="1"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="910">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -25854,7 +25862,7 @@
       <c r="Y910" s="1"/>
       <c r="Z910" s="1"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="911">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -25882,7 +25890,7 @@
       <c r="Y911" s="1"/>
       <c r="Z911" s="1"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="912">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -25910,7 +25918,7 @@
       <c r="Y912" s="1"/>
       <c r="Z912" s="1"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="913">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -25938,7 +25946,7 @@
       <c r="Y913" s="1"/>
       <c r="Z913" s="1"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="914">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -25966,7 +25974,7 @@
       <c r="Y914" s="1"/>
       <c r="Z914" s="1"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="915">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -25994,7 +26002,7 @@
       <c r="Y915" s="1"/>
       <c r="Z915" s="1"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="916">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -26022,7 +26030,7 @@
       <c r="Y916" s="1"/>
       <c r="Z916" s="1"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="917">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -26050,7 +26058,7 @@
       <c r="Y917" s="1"/>
       <c r="Z917" s="1"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="918">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -26078,7 +26086,7 @@
       <c r="Y918" s="1"/>
       <c r="Z918" s="1"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="919">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -26106,7 +26114,7 @@
       <c r="Y919" s="1"/>
       <c r="Z919" s="1"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="920">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -26134,7 +26142,7 @@
       <c r="Y920" s="1"/>
       <c r="Z920" s="1"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="921">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -26162,7 +26170,7 @@
       <c r="Y921" s="1"/>
       <c r="Z921" s="1"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="922">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -26190,7 +26198,7 @@
       <c r="Y922" s="1"/>
       <c r="Z922" s="1"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="923">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -26218,7 +26226,7 @@
       <c r="Y923" s="1"/>
       <c r="Z923" s="1"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="924">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -26246,7 +26254,7 @@
       <c r="Y924" s="1"/>
       <c r="Z924" s="1"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="925">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -26274,7 +26282,7 @@
       <c r="Y925" s="1"/>
       <c r="Z925" s="1"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="926">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -26302,7 +26310,7 @@
       <c r="Y926" s="1"/>
       <c r="Z926" s="1"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="927">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -26330,7 +26338,7 @@
       <c r="Y927" s="1"/>
       <c r="Z927" s="1"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="928">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -26358,7 +26366,7 @@
       <c r="Y928" s="1"/>
       <c r="Z928" s="1"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="929">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -26386,7 +26394,7 @@
       <c r="Y929" s="1"/>
       <c r="Z929" s="1"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="930">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -26414,7 +26422,7 @@
       <c r="Y930" s="1"/>
       <c r="Z930" s="1"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="931">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -26442,7 +26450,7 @@
       <c r="Y931" s="1"/>
       <c r="Z931" s="1"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="932">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -26470,7 +26478,7 @@
       <c r="Y932" s="1"/>
       <c r="Z932" s="1"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="933">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -26498,7 +26506,7 @@
       <c r="Y933" s="1"/>
       <c r="Z933" s="1"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="934">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -26526,7 +26534,7 @@
       <c r="Y934" s="1"/>
       <c r="Z934" s="1"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="935">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -26554,7 +26562,7 @@
       <c r="Y935" s="1"/>
       <c r="Z935" s="1"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="936">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -26582,7 +26590,7 @@
       <c r="Y936" s="1"/>
       <c r="Z936" s="1"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="937">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -26610,7 +26618,7 @@
       <c r="Y937" s="1"/>
       <c r="Z937" s="1"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="938">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -26638,7 +26646,7 @@
       <c r="Y938" s="1"/>
       <c r="Z938" s="1"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="939">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -26666,7 +26674,7 @@
       <c r="Y939" s="1"/>
       <c r="Z939" s="1"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="940">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -26694,7 +26702,7 @@
       <c r="Y940" s="1"/>
       <c r="Z940" s="1"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="941">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -26722,7 +26730,7 @@
       <c r="Y941" s="1"/>
       <c r="Z941" s="1"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="942">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -26750,7 +26758,7 @@
       <c r="Y942" s="1"/>
       <c r="Z942" s="1"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="943">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -26778,7 +26786,7 @@
       <c r="Y943" s="1"/>
       <c r="Z943" s="1"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="944">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -26806,7 +26814,7 @@
       <c r="Y944" s="1"/>
       <c r="Z944" s="1"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="945">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -26834,7 +26842,7 @@
       <c r="Y945" s="1"/>
       <c r="Z945" s="1"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="946">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -26862,7 +26870,7 @@
       <c r="Y946" s="1"/>
       <c r="Z946" s="1"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="947">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -26890,7 +26898,7 @@
       <c r="Y947" s="1"/>
       <c r="Z947" s="1"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="948">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -26918,7 +26926,7 @@
       <c r="Y948" s="1"/>
       <c r="Z948" s="1"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="949">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -26946,7 +26954,7 @@
       <c r="Y949" s="1"/>
       <c r="Z949" s="1"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="950">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -26974,7 +26982,7 @@
       <c r="Y950" s="1"/>
       <c r="Z950" s="1"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="951">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -27002,7 +27010,7 @@
       <c r="Y951" s="1"/>
       <c r="Z951" s="1"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="952">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -27030,7 +27038,7 @@
       <c r="Y952" s="1"/>
       <c r="Z952" s="1"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="953">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -27058,7 +27066,7 @@
       <c r="Y953" s="1"/>
       <c r="Z953" s="1"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="954">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -27086,7 +27094,7 @@
       <c r="Y954" s="1"/>
       <c r="Z954" s="1"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="955">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -27114,7 +27122,7 @@
       <c r="Y955" s="1"/>
       <c r="Z955" s="1"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="956">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -27142,7 +27150,7 @@
       <c r="Y956" s="1"/>
       <c r="Z956" s="1"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="957">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -27170,7 +27178,7 @@
       <c r="Y957" s="1"/>
       <c r="Z957" s="1"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="958">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -27198,7 +27206,7 @@
       <c r="Y958" s="1"/>
       <c r="Z958" s="1"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="959">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -27226,7 +27234,7 @@
       <c r="Y959" s="1"/>
       <c r="Z959" s="1"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="960">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -27254,7 +27262,7 @@
       <c r="Y960" s="1"/>
       <c r="Z960" s="1"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="961">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -27282,7 +27290,7 @@
       <c r="Y961" s="1"/>
       <c r="Z961" s="1"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="962">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -27310,7 +27318,7 @@
       <c r="Y962" s="1"/>
       <c r="Z962" s="1"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="963">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -27338,7 +27346,7 @@
       <c r="Y963" s="1"/>
       <c r="Z963" s="1"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="964">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -27366,7 +27374,7 @@
       <c r="Y964" s="1"/>
       <c r="Z964" s="1"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="965">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -27394,7 +27402,7 @@
       <c r="Y965" s="1"/>
       <c r="Z965" s="1"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="966">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -27422,7 +27430,7 @@
       <c r="Y966" s="1"/>
       <c r="Z966" s="1"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="967">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -27450,7 +27458,7 @@
       <c r="Y967" s="1"/>
       <c r="Z967" s="1"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="968">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -27478,7 +27486,7 @@
       <c r="Y968" s="1"/>
       <c r="Z968" s="1"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="969">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -27506,7 +27514,7 @@
       <c r="Y969" s="1"/>
       <c r="Z969" s="1"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="970">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -27534,7 +27542,7 @@
       <c r="Y970" s="1"/>
       <c r="Z970" s="1"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="971">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -27562,7 +27570,7 @@
       <c r="Y971" s="1"/>
       <c r="Z971" s="1"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="972">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -27590,7 +27598,7 @@
       <c r="Y972" s="1"/>
       <c r="Z972" s="1"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="973">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -27618,7 +27626,7 @@
       <c r="Y973" s="1"/>
       <c r="Z973" s="1"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="974">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -27646,7 +27654,7 @@
       <c r="Y974" s="1"/>
       <c r="Z974" s="1"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="975">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -27674,7 +27682,7 @@
       <c r="Y975" s="1"/>
       <c r="Z975" s="1"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="976">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -27702,7 +27710,7 @@
       <c r="Y976" s="1"/>
       <c r="Z976" s="1"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="977">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -27730,7 +27738,7 @@
       <c r="Y977" s="1"/>
       <c r="Z977" s="1"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="978">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -27758,7 +27766,7 @@
       <c r="Y978" s="1"/>
       <c r="Z978" s="1"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="979">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -27786,7 +27794,7 @@
       <c r="Y979" s="1"/>
       <c r="Z979" s="1"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="980">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -27814,7 +27822,7 @@
       <c r="Y980" s="1"/>
       <c r="Z980" s="1"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="981">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -27842,7 +27850,7 @@
       <c r="Y981" s="1"/>
       <c r="Z981" s="1"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="982">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -27870,7 +27878,7 @@
       <c r="Y982" s="1"/>
       <c r="Z982" s="1"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="983">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -27898,7 +27906,7 @@
       <c r="Y983" s="1"/>
       <c r="Z983" s="1"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="984">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -27926,7 +27934,7 @@
       <c r="Y984" s="1"/>
       <c r="Z984" s="1"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="985">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -27954,7 +27962,7 @@
       <c r="Y985" s="1"/>
       <c r="Z985" s="1"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="986">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -27982,7 +27990,7 @@
       <c r="Y986" s="1"/>
       <c r="Z986" s="1"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="987">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -28010,7 +28018,7 @@
       <c r="Y987" s="1"/>
       <c r="Z987" s="1"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="988">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -28038,7 +28046,7 @@
       <c r="Y988" s="1"/>
       <c r="Z988" s="1"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="989">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -28066,7 +28074,7 @@
       <c r="Y989" s="1"/>
       <c r="Z989" s="1"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="990">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -28094,7 +28102,7 @@
       <c r="Y990" s="1"/>
       <c r="Z990" s="1"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="991">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -28122,7 +28130,7 @@
       <c r="Y991" s="1"/>
       <c r="Z991" s="1"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="992">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -28150,7 +28158,7 @@
       <c r="Y992" s="1"/>
       <c r="Z992" s="1"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="993">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -28178,7 +28186,7 @@
       <c r="Y993" s="1"/>
       <c r="Z993" s="1"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="994">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -28206,7 +28214,7 @@
       <c r="Y994" s="1"/>
       <c r="Z994" s="1"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="995">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -28234,7 +28242,7 @@
       <c r="Y995" s="1"/>
       <c r="Z995" s="1"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="996">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -28262,7 +28270,7 @@
       <c r="Y996" s="1"/>
       <c r="Z996" s="1"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="997">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -28290,7 +28298,7 @@
       <c r="Y997" s="1"/>
       <c r="Z997" s="1"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="998">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -28318,7 +28326,7 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="999">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -28346,7 +28354,7 @@
       <c r="Y999" s="1"/>
       <c r="Z999" s="1"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row ht="15.75" customHeight="1" r="1000">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -28380,16 +28388,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.89"/>
-    <col customWidth="1" min="3" max="3" width="18.22"/>
-    <col customWidth="1" min="4" max="4" width="15.22"/>
-    <col customWidth="1" min="5" max="5" width="30.22"/>
+    <col min="1" max="1" width="14.89" customWidth="1"/>
+    <col min="3" max="3" width="18.22" customWidth="1"/>
+    <col min="4" max="4" width="15.22" customWidth="1"/>
+    <col min="5" max="5" width="30.22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28414,10 +28422,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="4">
-        <v>46154.72222222222</v>
+        <v>46154.7222222222</v>
       </c>
       <c r="D2" s="4">
-        <v>46154.76388888889</v>
+        <v>46154.7638888889</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
@@ -28428,10 +28436,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="4">
-        <v>46161.72222222222</v>
+        <v>46161.7222222222</v>
       </c>
       <c r="D3" s="4">
-        <v>46161.76388888889</v>
+        <v>46161.7638888889</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
@@ -28442,10 +28450,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="4">
-        <v>46168.72222222222</v>
+        <v>46168.7222222222</v>
       </c>
       <c r="D4" s="4">
-        <v>46168.76388888889</v>
+        <v>46168.7638888889</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>11</v>
@@ -28456,7 +28464,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4">
-        <v>46149.708333333336</v>
+        <v>46149.7083333333</v>
       </c>
       <c r="D5" s="4">
         <v>46149.75</v>
@@ -28470,10 +28478,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="4">
-        <v>46156.729166666664</v>
+        <v>46156.7291666666</v>
       </c>
       <c r="D6" s="4">
-        <v>46156.770833333336</v>
+        <v>46156.7708333333</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>13</v>
@@ -28484,7 +28492,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="4">
-        <v>46163.708333333336</v>
+        <v>46163.7083333333</v>
       </c>
       <c r="D7" s="4">
         <v>46163.75</v>
@@ -28498,7 +28506,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="4">
-        <v>46170.708333333336</v>
+        <v>46170.7083333333</v>
       </c>
       <c r="D8" s="4">
         <v>46170.75</v>
@@ -28512,7 +28520,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="4">
-        <v>46155.708333333336</v>
+        <v>46155.7083333333</v>
       </c>
       <c r="D9" s="4">
         <v>46155.75</v>
@@ -28529,10 +28537,10 @@
         <v>16</v>
       </c>
       <c r="C10" s="4">
-        <v>46162.708333333336</v>
+        <v>46162.7083333333</v>
       </c>
       <c r="D10" s="4">
-        <v>46162.739583333336</v>
+        <v>46162.7395833333</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>15</v>
@@ -28546,10 +28554,10 @@
         <v>16</v>
       </c>
       <c r="C11" s="4">
-        <v>46162.739583333336</v>
+        <v>46162.7395833333</v>
       </c>
       <c r="D11" s="4">
-        <v>46162.770833333336</v>
+        <v>46162.7708333333</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>15</v>
@@ -28560,7 +28568,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="4">
-        <v>46169.708333333336</v>
+        <v>46169.7083333333</v>
       </c>
       <c r="D12" s="4">
         <v>46169.75</v>
@@ -28574,10 +28582,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="4">
-        <v>46150.666666666664</v>
+        <v>46150.6666666667</v>
       </c>
       <c r="D13" s="4">
-        <v>46150.70138888889</v>
+        <v>46150.7013888889</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
@@ -28588,10 +28596,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="4">
-        <v>46157.666666666664</v>
+        <v>46157.6666666667</v>
       </c>
       <c r="D14" s="4">
-        <v>46157.70138888889</v>
+        <v>46157.7013888889</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
@@ -28602,10 +28610,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="4">
-        <v>46164.666666666664</v>
+        <v>46164.6666666667</v>
       </c>
       <c r="D15" s="4">
-        <v>46164.70138888889</v>
+        <v>46164.7013888889</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
@@ -28616,10 +28624,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="4">
-        <v>46171.666666666664</v>
+        <v>46171.6666666667</v>
       </c>
       <c r="D16" s="4">
-        <v>46171.70138888889</v>
+        <v>46171.7013888889</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>18</v>
@@ -28635,11 +28643,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -28654,6 +28662,9 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -28663,10 +28674,10 @@
         <v>20</v>
       </c>
       <c r="C2" s="4">
-        <v>46259.666666666664</v>
+        <v>46259.6666666667</v>
       </c>
       <c r="D2" s="4">
-        <v>46259.833333333336</v>
+        <v>46259.8333333333</v>
       </c>
     </row>
   </sheetData>
